--- a/3-multi-document-abbyy-vs-tiled3x1+docparse-paddleocr-paddlevl/test-results/page-level-excels/oocihm.N_00155_18750610/oocihm.N_00155_18750610.1.xlsx
+++ b/3-multi-document-abbyy-vs-tiled3x1+docparse-paddleocr-paddlevl/test-results/page-level-excels/oocihm.N_00155_18750610/oocihm.N_00155_18750610.1.xlsx
@@ -464,12 +464,12 @@
       </c>
       <c r="D1" s="1" t="inlineStr">
         <is>
-          <t>duplicate/tile overlap - paddle</t>
+          <t>Possible duplicate lines - paddle</t>
         </is>
       </c>
       <c r="E1" s="1" t="inlineStr">
         <is>
-          <t>duplicate/tile overlap - abbyy</t>
+          <t>Possible duplicate lines - abbyy</t>
         </is>
       </c>
       <c r="F1" s="1" t="inlineStr">
@@ -1031,7 +1031,7 @@
     <row r="7">
       <c r="A7" s="1" t="inlineStr">
         <is>
-          <t>duplicate/tile overlap issue count</t>
+          <t>Possible duplicate lines issue count</t>
         </is>
       </c>
       <c r="B7" s="1" t="inlineStr">

--- a/3-multi-document-abbyy-vs-tiled3x1+docparse-paddleocr-paddlevl/test-results/page-level-excels/oocihm.N_00155_18750610/oocihm.N_00155_18750610.1.xlsx
+++ b/3-multi-document-abbyy-vs-tiled3x1+docparse-paddleocr-paddlevl/test-results/page-level-excels/oocihm.N_00155_18750610/oocihm.N_00155_18750610.1.xlsx
@@ -416,14 +416,14 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:Y115"/>
+  <dimension ref="A1:Y53"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="39" customWidth="1" min="1" max="1"/>
     <col width="60" customWidth="1" min="2" max="2"/>
     <col width="60" customWidth="1" min="3" max="3"/>
     <col width="60" customWidth="1" min="4" max="4"/>
-    <col width="32" customWidth="1" min="5" max="5"/>
+    <col width="34" customWidth="1" min="5" max="5"/>
     <col width="60" customWidth="1" min="6" max="6"/>
     <col width="60" customWidth="1" min="7" max="7"/>
     <col width="60" customWidth="1" min="8" max="8"/>
@@ -431,7 +431,7 @@
     <col width="60" customWidth="1" min="10" max="10"/>
     <col width="60" customWidth="1" min="11" max="11"/>
     <col width="32" customWidth="1" min="12" max="12"/>
-    <col width="31" customWidth="1" min="13" max="13"/>
+    <col width="60" customWidth="1" min="13" max="13"/>
     <col width="60" customWidth="1" min="14" max="14"/>
     <col width="60" customWidth="1" min="15" max="15"/>
     <col width="60" customWidth="1" min="16" max="16"/>
@@ -581,12 +581,12 @@
       </c>
       <c r="B2" s="1" t="inlineStr">
         <is>
-          <t>C:\Users\BrittnyLapierre\Documents\OCR-Evaluations\3-multi-document-abbyy-vs-tiled3x1+docparse-paddleocr-paddlevl\test-data\preprocessing-tiling_3x1_dp+paddleocr+vl+clean\oocihm.N_00155_18750610\oocihm.N_00155_18750610.1.txt</t>
+          <t>3-multi-document-abbyy-vs-tiled3x1+docparse-paddleocr-paddlevl\test-data\preprocessing-tiling_3x1_dp+paddleocr+vl+clean\oocihm.N_00155_18750610\oocihm.N_00155_18750610.1.txt</t>
         </is>
       </c>
       <c r="C2" s="1" t="inlineStr">
         <is>
-          <t>C:\Users\BrittnyLapierre\Documents\OCR-Evaluations\3-multi-document-abbyy-vs-tiled3x1+docparse-paddleocr-paddlevl\test-data\abbyy\oocihm.N_00155_18750610\oocihm.N_00155_18750610.1.txt</t>
+          <t>3-multi-document-abbyy-vs-tiled3x1+docparse-paddleocr-paddlevl\test-data\abbyy\oocihm.N_00155_18750610\oocihm.N_00155_18750610.1.txt</t>
         </is>
       </c>
       <c r="D2" s="1" t="inlineStr">
@@ -602,7 +602,7 @@
       </c>
       <c r="G2" s="1" t="inlineStr">
         <is>
-          <t>L665: stray/suspicious non-ASCII glyph(s): U+20AC EURO SIGN | punctuation artifact: double/multiple hyphen; hyphen/bullet debris | suspicious token(s): kA1 (letter/digit mix) | localized OCR phrase divergence vs other OCR: "" vs "1914 11 1 kA1" :: you have held on the Great Western Railway, === :â€”1914 *~ 11 ---------1------** kA1</t>
+          <t>L665: punctuation artifact: double/multiple hyphen; hyphen/bullet debris | suspicious token(s): kA1 (letter/digit mix) | localized OCR phrase divergence vs other OCR: "" vs "1914 11 1 kA1" :: you have held on the Great Western Railway, === :—1914 *~ 11 ---------1------** kA1</t>
         </is>
       </c>
       <c r="H2" s="1" t="inlineStr">
@@ -617,16 +617,20 @@
       </c>
       <c r="J2" s="1" t="inlineStr">
         <is>
-          <t>L237: stray/suspicious non-ASCII glyph(s): U+20AC EURO SIGN :: act of diplomacy- â€” an achievement of the</t>
+          <t>L49: stray/suspicious non-ASCII glyph(s): U+FF1B FULLWIDTH SEMICOLON :: dominant, Catholic population ； and while the</t>
         </is>
       </c>
       <c r="K2" s="1" t="inlineStr">
         <is>
-          <t>L28: stray/suspicious non-ASCII glyph(s): U+20AC EURO SIGN :: ASSOCIATE CORONER.â€”Dr. Taylor, of Dun-</t>
+          <t>L1: BOM/control character at start of file | stray/suspicious non-ASCII glyph(s): U+FEFF ZERO WIDTH NO-BREAK SPACE | isolated marker/symbol line :: [BOM]</t>
         </is>
       </c>
       <c r="L2" s="1" t="inlineStr"/>
-      <c r="M2" s="1" t="inlineStr"/>
+      <c r="M2" s="1" t="inlineStr">
+        <is>
+          <t>L1: BOM/control character at start of file | stray/suspicious non-ASCII glyph(s): U+FEFF ZERO WIDTH NO-BREAK SPACE | isolated marker/symbol line :: [BOM]</t>
+        </is>
+      </c>
       <c r="N2" s="1" t="inlineStr">
         <is>
           <t>L1: isolated marker/symbol line :: T</t>
@@ -634,7 +638,7 @@
       </c>
       <c r="O2" s="1" t="inlineStr">
         <is>
-          <t>L1: isolated marker/symbol line :: ï»¿</t>
+          <t>L1: BOM/control character at start of file | stray/suspicious non-ASCII glyph(s): U+FEFF ZERO WIDTH NO-BREAK SPACE | isolated marker/symbol line :: [BOM]</t>
         </is>
       </c>
       <c r="P2" s="1" t="inlineStr">
@@ -685,7 +689,7 @@
       </c>
       <c r="C3" s="1" t="inlineStr">
         <is>
-          <t>2197</t>
+          <t>1984</t>
         </is>
       </c>
       <c r="D3" s="1" t="inlineStr">
@@ -701,7 +705,7 @@
       </c>
       <c r="G3" s="1" t="inlineStr">
         <is>
-          <t>L1340: stray/suspicious non-ASCII glyph(s): U+20AC EURO SIGN | localized OCR phrase divergence vs other OCR: "0ooinhabitantsgiving" vs "000 inhabitants giving" :: Vienna has about 900,000 inhabitantsâ€”giving</t>
+          <t>L1340: localized OCR phrase divergence vs other OCR: "0ooinhabitantsgiving" vs "000 inhabitants giving" :: Vienna has about 900,000 inhabitants—giving</t>
         </is>
       </c>
       <c r="H3" s="1" t="inlineStr">
@@ -711,17 +715,17 @@
       </c>
       <c r="I3" s="1" t="inlineStr">
         <is>
-          <t>L623: suspicious token(s): tunBte (odd internal casing) :: Complimentary Testimonial to Mr. E. O. tunBte that he was not mÂ°re seriously injured.</t>
+          <t>L623: suspicious token(s): tunBte (odd internal casing) :: Complimentary Testimonial to Mr. E. O. tunBte that he was not m°re seriously injured.</t>
         </is>
       </c>
       <c r="J3" s="1" t="inlineStr">
         <is>
-          <t>L454: stray/suspicious non-ASCII glyph(s): U+20AC EURO SIGN, U+00A6 BROKEN BAR | isolated marker/symbol line :: â€¦</t>
+          <t>L86: stray/suspicious non-ASCII glyph(s): U+7235 CJK UNIFIED IDEOGRAPH-7235 | isolated marker/symbol line :: 爵</t>
         </is>
       </c>
       <c r="K3" s="1" t="inlineStr">
         <is>
-          <t>L33: stray/suspicious non-ASCII glyph(s): U+20AC EURO SIGN, U+2122 TRADE MARK SIGN :: MAYORâ€™S COURT.â€”On Tuesday, John Clough</t>
+          <t>L142: stray/suspicious non-ASCII glyph(s): U+2022 BULLET :: tions of the German • army remained as an</t>
         </is>
       </c>
       <c r="L3" s="1" t="inlineStr"/>
@@ -743,7 +747,7 @@
       </c>
       <c r="Q3" s="1" t="inlineStr">
         <is>
-          <t>L663: stray/suspicious non-ASCII glyph(s): U+20AC EURO SIGN | punctuation artifact: repeated periods :: DEAR SIR.â€”Having heard with feelings of re.,-, â€” NT...3</t>
+          <t>L663: punctuation artifact: repeated periods :: DEAR SIR.—Having heard with feelings of re.,-, — NT...3</t>
         </is>
       </c>
       <c r="R3" s="1" t="inlineStr"/>
@@ -806,17 +810,17 @@
       </c>
       <c r="I4" s="1" t="inlineStr">
         <is>
-          <t>L665: stray/suspicious non-ASCII glyph(s): U+20AC EURO SIGN | punctuation artifact: double/multiple hyphen; hyphen/bullet debris | suspicious token(s): kA1 (letter/digit mix) | localized OCR phrase divergence vs other OCR: "" vs "1914 11 1 kA1" :: you have held on the Great Western Railway, === :â€”1914 *~ 11 ---------1------** kA1</t>
+          <t>L665: punctuation artifact: double/multiple hyphen; hyphen/bullet debris | suspicious token(s): kA1 (letter/digit mix) | localized OCR phrase divergence vs other OCR: "" vs "1914 11 1 kA1" :: you have held on the Great Western Railway, === :—1914 *~ 11 ---------1------** kA1</t>
         </is>
       </c>
       <c r="J4" s="1" t="inlineStr">
         <is>
-          <t>L455: stray/suspicious non-ASCII glyph(s): U+20AC EURO SIGN :: MAYOR's Court.â€”.â€” On Tuesday, John Clough</t>
+          <t>L139: stray/suspicious non-ASCII glyph(s): U+5FC3 CJK UNIFIED IDEOGRAPH-5FC3 | isolated marker/symbol line :: 心</t>
         </is>
       </c>
       <c r="K4" s="1" t="inlineStr">
         <is>
-          <t>L40: stray/suspicious non-ASCII glyph(s): U+20AC EURO SIGN :: !ACCIDENT.â€”On Monday afternoon last while</t>
+          <t>L230: stray/suspicious non-ASCII glyph(s): U+2022 BULLET | isolated marker/symbol line :: •</t>
         </is>
       </c>
       <c r="L4" s="1" t="inlineStr"/>
@@ -838,7 +842,7 @@
       </c>
       <c r="Q4" s="1" t="inlineStr">
         <is>
-          <t>L665: stray/suspicious non-ASCII glyph(s): U+20AC EURO SIGN | punctuation artifact: double/multiple hyphen; hyphen/bullet debris | suspicious token(s): kA1 (letter/digit mix) | localized OCR phrase divergence vs other OCR: "" vs "1914 11 1 kA1" :: you have held on the Great Western Railway, === :â€”1914 *~ 11 ---------1------** kA1</t>
+          <t>L665: punctuation artifact: double/multiple hyphen; hyphen/bullet debris | suspicious token(s): kA1 (letter/digit mix) | localized OCR phrase divergence vs other OCR: "" vs "1914 11 1 kA1" :: you have held on the Great Western Railway, === :—1914 *~ 11 ---------1------** kA1</t>
         </is>
       </c>
       <c r="R4" s="1" t="inlineStr"/>
@@ -856,7 +860,7 @@
       </c>
       <c r="W4" s="1" t="inlineStr">
         <is>
-          <t>L1559: stray/suspicious non-ASCII glyph(s): U+20AC EURO SIGN | abbreviation/spacing may be garbled :: cent.â€”i.e., only one word' in four is not of</t>
+          <t>L1559: abbreviation/spacing may be garbled :: cent.—i.e., only one word' in four is not of</t>
         </is>
       </c>
       <c r="X4" s="1" t="inlineStr"/>
@@ -870,12 +874,12 @@
       </c>
       <c r="B5" s="1" t="inlineStr">
         <is>
-          <t>111</t>
+          <t>102</t>
         </is>
       </c>
       <c r="C5" s="1" t="inlineStr">
         <is>
-          <t>145</t>
+          <t>43</t>
         </is>
       </c>
       <c r="D5" s="1" t="inlineStr">
@@ -897,17 +901,17 @@
       </c>
       <c r="I5" s="1" t="inlineStr">
         <is>
-          <t>L2075: suspicious token(s): AbES (odd internal casing) :: Â£AbES</t>
+          <t>L2075: suspicious token(s): AbES (odd internal casing) :: £AbES</t>
         </is>
       </c>
       <c r="J5" s="1" t="inlineStr">
         <is>
-          <t>L461: stray/suspicious non-ASCII glyph(s): U+20AC EURO SIGN :: Accident.â€”.- On Monday afternoon last while</t>
+          <t>L671: stray/suspicious non-ASCII glyph(s): U+4EAB CJK UNIFIED IDEOGRAPH-4EAB | isolated marker/symbol line :: 享</t>
         </is>
       </c>
       <c r="K5" s="1" t="inlineStr">
         <is>
-          <t>L65: stray/suspicious non-ASCII glyph(s): U+20AC EURO SIGN :: we are not privileged to knowâ€”the war fever</t>
+          <t>L232: stray/suspicious non-ASCII glyph(s): U+2022 BULLET | isolated marker/symbol line :: •</t>
         </is>
       </c>
       <c r="L5" s="1" t="inlineStr"/>
@@ -980,17 +984,17 @@
       </c>
       <c r="I6" s="1" t="inlineStr">
         <is>
-          <t>L2077: stray/suspicious non-ASCII glyph(s): U+20AC EURO SIGN | suspicious token(s): JanVIS (odd internal casing) :: FIRE AT JanVIS.â€”Yesterday afternoon be-</t>
+          <t>L2077: suspicious token(s): JanVIS (odd internal casing) :: FIRE AT JanVIS.—Yesterday afternoon be-</t>
         </is>
       </c>
       <c r="J6" s="1" t="inlineStr">
         <is>
-          <t>L491: stray/suspicious non-ASCII glyph(s): U+20AC EURO SIGN :: LYNDEN.â€” The Vocal and Instrumental</t>
+          <t>L1141: stray/suspicious non-ASCII glyph(s): U+590F CJK UNIFIED IDEOGRAPH-590F :: One of the Parties 夏 Implicated Arrested</t>
         </is>
       </c>
       <c r="K6" s="1" t="inlineStr">
         <is>
-          <t>L67: stray/suspicious non-ASCII glyph(s): U+20AC EURO SIGN :: rumor that the Cabinet at Berlinâ€”or perhaps</t>
+          <t>L680: stray/suspicious non-ASCII glyph(s): U+00A5 YEN SIGN :: ment of the late Finance ¥initer of Canada,</t>
         </is>
       </c>
       <c r="L6" s="1" t="inlineStr"/>
@@ -1002,7 +1006,7 @@
       </c>
       <c r="O6" s="1" t="inlineStr">
         <is>
-          <t>L230: stray/suspicious non-ASCII glyph(s): U+20AC EURO SIGN, U+00A2 CENT SIGN | isolated marker/symbol line :: â€¢</t>
+          <t>L230: stray/suspicious non-ASCII glyph(s): U+2022 BULLET | isolated marker/symbol line :: •</t>
         </is>
       </c>
       <c r="P6" s="1" t="inlineStr">
@@ -1063,17 +1067,17 @@
       </c>
       <c r="I7" s="1" t="inlineStr">
         <is>
-          <t>L2190: stray/suspicious non-ASCII glyph(s): U+20AC EURO SIGN, U+2122 TRADE MARK SIGN | suspicious token(s): 1cellency (letter/digit mix) :: hands of a Government the power of nomi-1cellencyâ€™s advisers responsible for whatever</t>
+          <t>L2190: suspicious token(s): 1cellency’s (letter/digit mix) :: hands of a Government the power of nomi-1cellency’s advisers responsible for whatever</t>
         </is>
       </c>
       <c r="J7" s="1" t="inlineStr">
         <is>
-          <t>L634: stray/suspicious non-ASCII glyph(s): U+20AC EURO SIGN :: â€œEngland."</t>
+          <t>L1177: stray/suspicious non-ASCII glyph(s): U+3002 IDEOGRAPHIC FULL STOP | isolated marker/symbol line :: 。</t>
         </is>
       </c>
       <c r="K7" s="1" t="inlineStr">
         <is>
-          <t>L69: stray/suspicious non-ASCII glyph(s): U+20AC EURO SIGN :: marckâ€”had forwarded a note to the French</t>
+          <t>L1813: stray/suspicious non-ASCII glyph(s): U+2022 BULLET :: halters.•</t>
         </is>
       </c>
       <c r="L7" s="1" t="inlineStr"/>
@@ -1085,7 +1089,7 @@
       </c>
       <c r="O7" s="1" t="inlineStr">
         <is>
-          <t>L232: stray/suspicious non-ASCII glyph(s): U+20AC EURO SIGN, U+00A2 CENT SIGN | isolated marker/symbol line :: â€¢</t>
+          <t>L232: stray/suspicious non-ASCII glyph(s): U+2022 BULLET | isolated marker/symbol line :: •</t>
         </is>
       </c>
       <c r="P7" s="1" t="inlineStr">
@@ -1147,12 +1151,12 @@
       <c r="I8" s="1" t="inlineStr"/>
       <c r="J8" s="1" t="inlineStr">
         <is>
-          <t>L743: stray/suspicious non-ASCII glyph(s): U+20AC EURO SIGN, U+FFFD REPLACEMENT CHARACTER :: This ã€� rat</t>
+          <t>L1287: stray/suspicious non-ASCII glyph(s): U+5FC3 CJK UNIFIED IDEOGRAPH-5FC3 | isolated marker/symbol line :: 心</t>
         </is>
       </c>
       <c r="K8" s="1" t="inlineStr">
         <is>
-          <t>L78: stray/suspicious non-ASCII glyph(s): U+20AC EURO SIGN, U+02DC SMALL TILDE :: â€˜* for apprehension that the peace of Europe</t>
+          <t>L2194: stray/suspicious non-ASCII glyph(s): U+2022 BULLET | isolated marker/symbol line :: •</t>
         </is>
       </c>
       <c r="L8" s="1" t="inlineStr"/>
@@ -1222,14 +1226,10 @@
       <c r="I9" s="1" t="inlineStr"/>
       <c r="J9" s="1" t="inlineStr">
         <is>
-          <t>L1022: stray/suspicious non-ASCII glyph(s): U+20AC EURO SIGN :: about 8,000 words â€” counting as distinct</t>
-        </is>
-      </c>
-      <c r="K9" s="1" t="inlineStr">
-        <is>
-          <t>L80: stray/suspicious non-ASCII glyph(s): U+20AC EURO SIGN :: â€”although German journals have, since the</t>
-        </is>
-      </c>
+          <t>L1460: stray/suspicious non-ASCII glyph(s): U+3002 IDEOGRAPHIC FULL STOP | isolated marker/symbol line :: 。</t>
+        </is>
+      </c>
+      <c r="K9" s="1" t="inlineStr"/>
       <c r="L9" s="1" t="inlineStr"/>
       <c r="M9" s="1" t="inlineStr"/>
       <c r="N9" s="1" t="inlineStr">
@@ -1269,12 +1269,12 @@
       </c>
       <c r="B10" s="1" t="inlineStr">
         <is>
-          <t>20</t>
+          <t>11</t>
         </is>
       </c>
       <c r="C10" s="1" t="inlineStr">
         <is>
-          <t>114</t>
+          <t>7</t>
         </is>
       </c>
       <c r="D10" s="1" t="inlineStr"/>
@@ -1293,19 +1293,15 @@
       <c r="I10" s="1" t="inlineStr"/>
       <c r="J10" s="1" t="inlineStr">
         <is>
-          <t>L1039: stray/suspicious non-ASCII glyph(s): U+20AC EURO SIGN :: 15,000 are not of old English stockâ€”a pro-</t>
-        </is>
-      </c>
-      <c r="K10" s="1" t="inlineStr">
-        <is>
-          <t>L85: stray/suspicious non-ASCII glyph(s): U+20AC EURO SIGN :: once characterized their neighborsâ€”has</t>
-        </is>
-      </c>
+          <t>L1813: stray/suspicious non-ASCII glyph(s): U+FF1B FULLWIDTH SEMICOLON :: Dick?" No, no, Brother Jones ； no chick-</t>
+        </is>
+      </c>
+      <c r="K10" s="1" t="inlineStr"/>
       <c r="L10" s="1" t="inlineStr"/>
       <c r="M10" s="1" t="inlineStr"/>
       <c r="N10" s="1" t="inlineStr">
         <is>
-          <t>L126: symbol-only separator/garbage line :: 10,</t>
+          <t>L86: stray/suspicious non-ASCII glyph(s): U+7235 CJK UNIFIED IDEOGRAPH-7235 | isolated marker/symbol line :: 爵</t>
         </is>
       </c>
       <c r="O10" s="1" t="inlineStr">
@@ -1345,7 +1341,7 @@
       </c>
       <c r="C11" s="1" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>1</t>
         </is>
       </c>
       <c r="D11" s="1" t="inlineStr"/>
@@ -1364,19 +1360,15 @@
       <c r="I11" s="1" t="inlineStr"/>
       <c r="J11" s="1" t="inlineStr">
         <is>
-          <t>L1044: stray/suspicious non-ASCII glyph(s): U+20AC EURO SIGN :: non-English element is about two-wordsâ€”â€”</t>
-        </is>
-      </c>
-      <c r="K11" s="1" t="inlineStr">
-        <is>
-          <t>L88: stray/suspicious non-ASCII glyph(s): U+20AC EURO SIGN :: be assigned for thisâ€”some internal, others</t>
-        </is>
-      </c>
+          <t>L1829: stray/suspicious non-ASCII glyph(s): U+3002 IDEOGRAPHIC FULL STOP | isolated marker/symbol line :: 。</t>
+        </is>
+      </c>
+      <c r="K11" s="1" t="inlineStr"/>
       <c r="L11" s="1" t="inlineStr"/>
       <c r="M11" s="1" t="inlineStr"/>
       <c r="N11" s="1" t="inlineStr">
         <is>
-          <t>L299: isolated marker/symbol line :: 7</t>
+          <t>L126: symbol-only separator/garbage line :: 10,</t>
         </is>
       </c>
       <c r="O11" s="1" t="inlineStr">
@@ -1411,7 +1403,7 @@
       </c>
       <c r="B12" s="1" t="inlineStr">
         <is>
-          <t>48</t>
+          <t>52</t>
         </is>
       </c>
       <c r="C12" s="1" t="inlineStr">
@@ -1435,19 +1427,15 @@
       <c r="I12" s="1" t="inlineStr"/>
       <c r="J12" s="1" t="inlineStr">
         <is>
-          <t>L1092: stray/suspicious non-ASCII glyph(s): U+20AC EURO SIGN :: IV., is on the whole about 85 â€” 80 being the</t>
-        </is>
-      </c>
-      <c r="K12" s="1" t="inlineStr">
-        <is>
-          <t>L99: stray/suspicious non-ASCII glyph(s): U+20AC EURO SIGN, U+FFFD REPLACEMENT CHARACTER :: the man of â€œ blood and ironâ€� has laid a</t>
-        </is>
-      </c>
+          <t>L2029: stray/suspicious non-ASCII glyph(s): U+2192 RIGHTWARDS ARROW | isolated marker/symbol line :: →</t>
+        </is>
+      </c>
+      <c r="K12" s="1" t="inlineStr"/>
       <c r="L12" s="1" t="inlineStr"/>
       <c r="M12" s="1" t="inlineStr"/>
       <c r="N12" s="1" t="inlineStr">
         <is>
-          <t>L454: stray/suspicious non-ASCII glyph(s): U+20AC EURO SIGN, U+00A6 BROKEN BAR | isolated marker/symbol line :: â€¦</t>
+          <t>L139: stray/suspicious non-ASCII glyph(s): U+5FC3 CJK UNIFIED IDEOGRAPH-5FC3 | isolated marker/symbol line :: 心</t>
         </is>
       </c>
       <c r="O12" s="1" t="inlineStr">
@@ -1488,21 +1476,13 @@
       <c r="G13" s="1" t="inlineStr"/>
       <c r="H13" s="1" t="inlineStr"/>
       <c r="I13" s="1" t="inlineStr"/>
-      <c r="J13" s="1" t="inlineStr">
-        <is>
-          <t>L1141: stray/suspicious non-ASCII glyph(s): U+00A4 CURRENCY SIGN, U+FFFD REPLACEMENT CHARACTER :: One of the Parties å¤� Implicated Arrested</t>
-        </is>
-      </c>
-      <c r="K13" s="1" t="inlineStr">
-        <is>
-          <t>L105: stray/suspicious non-ASCII glyph(s): U+20AC EURO SIGN :: Laud so much admiredâ€”albeit, a minister of</t>
-        </is>
-      </c>
+      <c r="J13" s="1" t="inlineStr"/>
+      <c r="K13" s="1" t="inlineStr"/>
       <c r="L13" s="1" t="inlineStr"/>
       <c r="M13" s="1" t="inlineStr"/>
       <c r="N13" s="1" t="inlineStr">
         <is>
-          <t>L516: isolated marker/symbol line :: C</t>
+          <t>L299: isolated marker/symbol line :: 7</t>
         </is>
       </c>
       <c r="O13" s="1" t="inlineStr">
@@ -1543,21 +1523,13 @@
       <c r="G14" s="1" t="inlineStr"/>
       <c r="H14" s="1" t="inlineStr"/>
       <c r="I14" s="1" t="inlineStr"/>
-      <c r="J14" s="1" t="inlineStr">
-        <is>
-          <t>L1177: stray/suspicious non-ASCII glyph(s): U+20AC EURO SIGN | isolated marker/symbol line :: ã€‚</t>
-        </is>
-      </c>
-      <c r="K14" s="1" t="inlineStr">
-        <is>
-          <t>L106: stray/suspicious non-ASCII glyph(s): U+20AC EURO SIGN :: the Gospel of Peaceâ€”and which, under its</t>
-        </is>
-      </c>
+      <c r="J14" s="1" t="inlineStr"/>
+      <c r="K14" s="1" t="inlineStr"/>
       <c r="L14" s="1" t="inlineStr"/>
       <c r="M14" s="1" t="inlineStr"/>
       <c r="N14" s="1" t="inlineStr">
         <is>
-          <t>L519: isolated marker/symbol line :: :</t>
+          <t>L454: isolated marker/symbol line :: …</t>
         </is>
       </c>
       <c r="O14" s="1" t="inlineStr">
@@ -1598,21 +1570,13 @@
       <c r="G15" s="1" t="inlineStr"/>
       <c r="H15" s="1" t="inlineStr"/>
       <c r="I15" s="1" t="inlineStr"/>
-      <c r="J15" s="1" t="inlineStr">
-        <is>
-          <t>L1379: stray/suspicious non-ASCII glyph(s): U+20AC EURO SIGN :: Canada is, by the people.â€œAll questions of</t>
-        </is>
-      </c>
-      <c r="K15" s="1" t="inlineStr">
-        <is>
-          <t>L142: stray/suspicious non-ASCII glyph(s): U+20AC EURO SIGN, U+00A2 CENT SIGN :: tions of the German â€¢ army remained as an</t>
-        </is>
-      </c>
+      <c r="J15" s="1" t="inlineStr"/>
+      <c r="K15" s="1" t="inlineStr"/>
       <c r="L15" s="1" t="inlineStr"/>
       <c r="M15" s="1" t="inlineStr"/>
       <c r="N15" s="1" t="inlineStr">
         <is>
-          <t>L520: isolated marker/symbol line :: 2</t>
+          <t>L516: isolated marker/symbol line :: C</t>
         </is>
       </c>
       <c r="O15" s="1" t="inlineStr">
@@ -1653,21 +1617,13 @@
       <c r="G16" s="1" t="inlineStr"/>
       <c r="H16" s="1" t="inlineStr"/>
       <c r="I16" s="1" t="inlineStr"/>
-      <c r="J16" s="1" t="inlineStr">
-        <is>
-          <t>L1460: stray/suspicious non-ASCII glyph(s): U+20AC EURO SIGN | isolated marker/symbol line :: ã€‚</t>
-        </is>
-      </c>
-      <c r="K16" s="1" t="inlineStr">
-        <is>
-          <t>L158: stray/suspicious non-ASCII glyph(s): U+20AC EURO SIGN :: â€”the re-organization of her army has been</t>
-        </is>
-      </c>
+      <c r="J16" s="1" t="inlineStr"/>
+      <c r="K16" s="1" t="inlineStr"/>
       <c r="L16" s="1" t="inlineStr"/>
       <c r="M16" s="1" t="inlineStr"/>
       <c r="N16" s="1" t="inlineStr">
         <is>
-          <t>L521: isolated marker/symbol line :: -</t>
+          <t>L519: isolated marker/symbol line :: :</t>
         </is>
       </c>
       <c r="O16" s="1" t="inlineStr">
@@ -1708,21 +1664,13 @@
       <c r="G17" s="1" t="inlineStr"/>
       <c r="H17" s="1" t="inlineStr"/>
       <c r="I17" s="1" t="inlineStr"/>
-      <c r="J17" s="1" t="inlineStr">
-        <is>
-          <t>L1633: stray/suspicious non-ASCII glyph(s): U+20AC EURO SIGN :: senseâ€”and on some topics of great sense-</t>
-        </is>
-      </c>
-      <c r="K17" s="1" t="inlineStr">
-        <is>
-          <t>L230: stray/suspicious non-ASCII glyph(s): U+20AC EURO SIGN, U+00A2 CENT SIGN | isolated marker/symbol line :: â€¢</t>
-        </is>
-      </c>
+      <c r="J17" s="1" t="inlineStr"/>
+      <c r="K17" s="1" t="inlineStr"/>
       <c r="L17" s="1" t="inlineStr"/>
       <c r="M17" s="1" t="inlineStr"/>
       <c r="N17" s="1" t="inlineStr">
         <is>
-          <t>L618: isolated marker/symbol line :: 8</t>
+          <t>L520: isolated marker/symbol line :: 2</t>
         </is>
       </c>
       <c r="O17" s="1" t="inlineStr">
@@ -1751,21 +1699,13 @@
       <c r="G18" s="1" t="inlineStr"/>
       <c r="H18" s="1" t="inlineStr"/>
       <c r="I18" s="1" t="inlineStr"/>
-      <c r="J18" s="1" t="inlineStr">
-        <is>
-          <t>L1634: stray/suspicious non-ASCII glyph(s): U+20AC EURO SIGN :: to ourselves â€” less freedom of talk and</t>
-        </is>
-      </c>
-      <c r="K18" s="1" t="inlineStr">
-        <is>
-          <t>L232: stray/suspicious non-ASCII glyph(s): U+20AC EURO SIGN, U+00A2 CENT SIGN | isolated marker/symbol line :: â€¢</t>
-        </is>
-      </c>
+      <c r="J18" s="1" t="inlineStr"/>
+      <c r="K18" s="1" t="inlineStr"/>
       <c r="L18" s="1" t="inlineStr"/>
       <c r="M18" s="1" t="inlineStr"/>
       <c r="N18" s="1" t="inlineStr">
         <is>
-          <t>L670: isolated marker/symbol line :: 8</t>
+          <t>L521: isolated marker/symbol line :: -</t>
         </is>
       </c>
       <c r="O18" s="1" t="inlineStr">
@@ -1794,21 +1734,13 @@
       <c r="G19" s="1" t="inlineStr"/>
       <c r="H19" s="1" t="inlineStr"/>
       <c r="I19" s="1" t="inlineStr"/>
-      <c r="J19" s="1" t="inlineStr">
-        <is>
-          <t>L1704: stray/suspicious non-ASCII glyph(s): U+20AC EURO SIGN :: vised â€” arid one had been devised, although</t>
-        </is>
-      </c>
-      <c r="K19" s="1" t="inlineStr">
-        <is>
-          <t>L254: stray/suspicious non-ASCII glyph(s): U+20AC EURO SIGN :: VOL. XVIII.â€”NO. 23.</t>
-        </is>
-      </c>
+      <c r="J19" s="1" t="inlineStr"/>
+      <c r="K19" s="1" t="inlineStr"/>
       <c r="L19" s="1" t="inlineStr"/>
       <c r="M19" s="1" t="inlineStr"/>
       <c r="N19" s="1" t="inlineStr">
         <is>
-          <t>L909: isolated marker/symbol line :: 3</t>
+          <t>L618: isolated marker/symbol line :: 8</t>
         </is>
       </c>
       <c r="O19" s="1" t="inlineStr">
@@ -1837,26 +1769,18 @@
       <c r="G20" s="1" t="inlineStr"/>
       <c r="H20" s="1" t="inlineStr"/>
       <c r="I20" s="1" t="inlineStr"/>
-      <c r="J20" s="1" t="inlineStr">
-        <is>
-          <t>L1829: stray/suspicious non-ASCII glyph(s): U+20AC EURO SIGN | isolated marker/symbol line :: ã€‚</t>
-        </is>
-      </c>
-      <c r="K20" s="1" t="inlineStr">
-        <is>
-          <t>L461: stray/suspicious non-ASCII glyph(s): U+20AC EURO SIGN :: your duty, do it ; you must "â€”would be to</t>
-        </is>
-      </c>
+      <c r="J20" s="1" t="inlineStr"/>
+      <c r="K20" s="1" t="inlineStr"/>
       <c r="L20" s="1" t="inlineStr"/>
       <c r="M20" s="1" t="inlineStr"/>
       <c r="N20" s="1" t="inlineStr">
         <is>
-          <t>L910: isolated marker/symbol line :: %</t>
+          <t>L670: isolated marker/symbol line :: 8</t>
         </is>
       </c>
       <c r="O20" s="1" t="inlineStr">
         <is>
-          <t>L2194: stray/suspicious non-ASCII glyph(s): U+20AC EURO SIGN, U+00A2 CENT SIGN | isolated marker/symbol line :: â€¢</t>
+          <t>L2194: stray/suspicious non-ASCII glyph(s): U+2022 BULLET | isolated marker/symbol line :: •</t>
         </is>
       </c>
       <c r="P20" s="1" t="inlineStr"/>
@@ -1880,21 +1804,13 @@
       <c r="G21" s="1" t="inlineStr"/>
       <c r="H21" s="1" t="inlineStr"/>
       <c r="I21" s="1" t="inlineStr"/>
-      <c r="J21" s="1" t="inlineStr">
-        <is>
-          <t>L1950: stray/suspicious non-ASCII glyph(s): U+20AC EURO SIGN, U+FFFD REPLACEMENT CHARACTER :: When you tell a horse to " get upâ€� look</t>
-        </is>
-      </c>
-      <c r="K21" s="1" t="inlineStr">
-        <is>
-          <t>L481: stray/suspicious non-ASCII glyph(s): U+20AC EURO SIGN :: visedâ€”and one had been devised, although</t>
-        </is>
-      </c>
+      <c r="J21" s="1" t="inlineStr"/>
+      <c r="K21" s="1" t="inlineStr"/>
       <c r="L21" s="1" t="inlineStr"/>
       <c r="M21" s="1" t="inlineStr"/>
       <c r="N21" s="1" t="inlineStr">
         <is>
-          <t>L1176: isolated marker/symbol line :: 0</t>
+          <t>L671: stray/suspicious non-ASCII glyph(s): U+4EAB CJK UNIFIED IDEOGRAPH-4EAB | isolated marker/symbol line :: 享</t>
         </is>
       </c>
       <c r="O21" s="1" t="inlineStr"/>
@@ -1920,16 +1836,12 @@
       <c r="H22" s="1" t="inlineStr"/>
       <c r="I22" s="1" t="inlineStr"/>
       <c r="J22" s="1" t="inlineStr"/>
-      <c r="K22" s="1" t="inlineStr">
-        <is>
-          <t>L573: stray/suspicious non-ASCII glyph(s): U+20AC EURO SIGN, U+2122 TRADE MARK SIGN :: oâ€™clock, to receive nominations, according to</t>
-        </is>
-      </c>
+      <c r="K22" s="1" t="inlineStr"/>
       <c r="L22" s="1" t="inlineStr"/>
       <c r="M22" s="1" t="inlineStr"/>
       <c r="N22" s="1" t="inlineStr">
         <is>
-          <t>L1177: stray/suspicious non-ASCII glyph(s): U+20AC EURO SIGN | isolated marker/symbol line :: ã€‚</t>
+          <t>L909: isolated marker/symbol line :: 3</t>
         </is>
       </c>
       <c r="O22" s="1" t="inlineStr"/>
@@ -1955,16 +1867,12 @@
       <c r="H23" s="1" t="inlineStr"/>
       <c r="I23" s="1" t="inlineStr"/>
       <c r="J23" s="1" t="inlineStr"/>
-      <c r="K23" s="1" t="inlineStr">
-        <is>
-          <t>L580: stray/suspicious non-ASCII glyph(s): U+20AC EURO SIGN :: a meetingâ€”Mr. Bruce in the chair.</t>
-        </is>
-      </c>
+      <c r="K23" s="1" t="inlineStr"/>
       <c r="L23" s="1" t="inlineStr"/>
       <c r="M23" s="1" t="inlineStr"/>
       <c r="N23" s="1" t="inlineStr">
         <is>
-          <t>L1178: isolated marker/symbol line :: 4</t>
+          <t>L910: isolated marker/symbol line :: %</t>
         </is>
       </c>
       <c r="O23" s="1" t="inlineStr"/>
@@ -1990,16 +1898,12 @@
       <c r="H24" s="1" t="inlineStr"/>
       <c r="I24" s="1" t="inlineStr"/>
       <c r="J24" s="1" t="inlineStr"/>
-      <c r="K24" s="1" t="inlineStr">
-        <is>
-          <t>L583: stray/suspicious non-ASCII glyph(s): U+20AC EURO SIGN :: address the.meeting. He saidâ€”It had not</t>
-        </is>
-      </c>
+      <c r="K24" s="1" t="inlineStr"/>
       <c r="L24" s="1" t="inlineStr"/>
       <c r="M24" s="1" t="inlineStr"/>
       <c r="N24" s="1" t="inlineStr">
         <is>
-          <t>L1193: isolated marker/symbol line :: 1</t>
+          <t>L1176: isolated marker/symbol line :: 0</t>
         </is>
       </c>
       <c r="O24" s="1" t="inlineStr"/>
@@ -2025,16 +1929,12 @@
       <c r="H25" s="1" t="inlineStr"/>
       <c r="I25" s="1" t="inlineStr"/>
       <c r="J25" s="1" t="inlineStr"/>
-      <c r="K25" s="1" t="inlineStr">
-        <is>
-          <t>L641: stray/suspicious non-ASCII glyph(s): U+20AC EURO SIGN, U+2122 TRADE MARK SIGN :: WHATâ€™S IN A NAME?â€”Mr. Just, lately ac-</t>
-        </is>
-      </c>
+      <c r="K25" s="1" t="inlineStr"/>
       <c r="L25" s="1" t="inlineStr"/>
       <c r="M25" s="1" t="inlineStr"/>
       <c r="N25" s="1" t="inlineStr">
         <is>
-          <t>L1278: isolated marker/symbol line :: 2</t>
+          <t>L1177: stray/suspicious non-ASCII glyph(s): U+3002 IDEOGRAPHIC FULL STOP | isolated marker/symbol line :: 。</t>
         </is>
       </c>
       <c r="O25" s="1" t="inlineStr"/>
@@ -2060,16 +1960,12 @@
       <c r="H26" s="1" t="inlineStr"/>
       <c r="I26" s="1" t="inlineStr"/>
       <c r="J26" s="1" t="inlineStr"/>
-      <c r="K26" s="1" t="inlineStr">
-        <is>
-          <t>L663: stray/suspicious non-ASCII glyph(s): U+20AC EURO SIGN | punctuation artifact: repeated periods :: DEAR SIR.â€”Having heard with feelings of re.,-, â€” NT...3</t>
-        </is>
-      </c>
+      <c r="K26" s="1" t="inlineStr"/>
       <c r="L26" s="1" t="inlineStr"/>
       <c r="M26" s="1" t="inlineStr"/>
       <c r="N26" s="1" t="inlineStr">
         <is>
-          <t>L1279: isolated marker/symbol line :: 4</t>
+          <t>L1178: isolated marker/symbol line :: 4</t>
         </is>
       </c>
       <c r="O26" s="1" t="inlineStr"/>
@@ -2095,16 +1991,12 @@
       <c r="H27" s="1" t="inlineStr"/>
       <c r="I27" s="1" t="inlineStr"/>
       <c r="J27" s="1" t="inlineStr"/>
-      <c r="K27" s="1" t="inlineStr">
-        <is>
-          <t>L665: stray/suspicious non-ASCII glyph(s): U+20AC EURO SIGN | punctuation artifact: double/multiple hyphen; hyphen/bullet debris | suspicious token(s): kA1 (letter/digit mix) | localized OCR phrase divergence vs other OCR: "" vs "1914 11 1 kA1" :: you have held on the Great Western Railway, === :â€”1914 *~ 11 ---------1------** kA1</t>
-        </is>
-      </c>
+      <c r="K27" s="1" t="inlineStr"/>
       <c r="L27" s="1" t="inlineStr"/>
       <c r="M27" s="1" t="inlineStr"/>
       <c r="N27" s="1" t="inlineStr">
         <is>
-          <t>L1288: isolated marker/symbol line :: -</t>
+          <t>L1193: isolated marker/symbol line :: 1</t>
         </is>
       </c>
       <c r="O27" s="1" t="inlineStr"/>
@@ -2130,16 +2022,12 @@
       <c r="H28" s="1" t="inlineStr"/>
       <c r="I28" s="1" t="inlineStr"/>
       <c r="J28" s="1" t="inlineStr"/>
-      <c r="K28" s="1" t="inlineStr">
-        <is>
-          <t>L680: stray/suspicious non-ASCII glyph(s): U+00A5 YEN SIGN :: ment of the late Finance Â¥initer of Canada,</t>
-        </is>
-      </c>
+      <c r="K28" s="1" t="inlineStr"/>
       <c r="L28" s="1" t="inlineStr"/>
       <c r="M28" s="1" t="inlineStr"/>
       <c r="N28" s="1" t="inlineStr">
         <is>
-          <t>L1289: isolated marker/symbol line :: E</t>
+          <t>L1278: isolated marker/symbol line :: 2</t>
         </is>
       </c>
       <c r="O28" s="1" t="inlineStr"/>
@@ -2165,16 +2053,12 @@
       <c r="H29" s="1" t="inlineStr"/>
       <c r="I29" s="1" t="inlineStr"/>
       <c r="J29" s="1" t="inlineStr"/>
-      <c r="K29" s="1" t="inlineStr">
-        <is>
-          <t>L726: stray/suspicious non-ASCII glyph(s): U+20AC EURO SIGN, U+FFFD REPLACEMENT CHARACTER :: that he " captured ?â€� Mr. Mackenzie, or how</t>
-        </is>
-      </c>
+      <c r="K29" s="1" t="inlineStr"/>
       <c r="L29" s="1" t="inlineStr"/>
       <c r="M29" s="1" t="inlineStr"/>
       <c r="N29" s="1" t="inlineStr">
         <is>
-          <t>L1290: isolated marker/symbol line :: C</t>
+          <t>L1279: isolated marker/symbol line :: 4</t>
         </is>
       </c>
       <c r="O29" s="1" t="inlineStr"/>
@@ -2200,16 +2084,12 @@
       <c r="H30" s="1" t="inlineStr"/>
       <c r="I30" s="1" t="inlineStr"/>
       <c r="J30" s="1" t="inlineStr"/>
-      <c r="K30" s="1" t="inlineStr">
-        <is>
-          <t>L727: stray/suspicious non-ASCII glyph(s): U+20AC EURO SIGN, U+FFFD REPLACEMENT CHARACTER :: the latter " capturedâ€� him. Knowing as they</t>
-        </is>
-      </c>
+      <c r="K30" s="1" t="inlineStr"/>
       <c r="L30" s="1" t="inlineStr"/>
       <c r="M30" s="1" t="inlineStr"/>
       <c r="N30" s="1" t="inlineStr">
         <is>
-          <t>L1291: isolated marker/symbol line :: W</t>
+          <t>L1287: stray/suspicious non-ASCII glyph(s): U+5FC3 CJK UNIFIED IDEOGRAPH-5FC3 | isolated marker/symbol line :: 心</t>
         </is>
       </c>
       <c r="O30" s="1" t="inlineStr"/>
@@ -2235,16 +2115,12 @@
       <c r="H31" s="1" t="inlineStr"/>
       <c r="I31" s="1" t="inlineStr"/>
       <c r="J31" s="1" t="inlineStr"/>
-      <c r="K31" s="1" t="inlineStr">
-        <is>
-          <t>L779: stray/suspicious non-ASCII glyph(s): U+20AC EURO SIGN, U+02DC SMALL TILDE :: claims to find are used withâ€˜less freedom</t>
-        </is>
-      </c>
+      <c r="K31" s="1" t="inlineStr"/>
       <c r="L31" s="1" t="inlineStr"/>
       <c r="M31" s="1" t="inlineStr"/>
       <c r="N31" s="1" t="inlineStr">
         <is>
-          <t>L1337: isolated marker/symbol line :: s</t>
+          <t>L1288: isolated marker/symbol line :: -</t>
         </is>
       </c>
       <c r="O31" s="1" t="inlineStr"/>
@@ -2270,16 +2146,12 @@
       <c r="H32" s="1" t="inlineStr"/>
       <c r="I32" s="1" t="inlineStr"/>
       <c r="J32" s="1" t="inlineStr"/>
-      <c r="K32" s="1" t="inlineStr">
-        <is>
-          <t>L785: stray/suspicious non-ASCII glyph(s): U+20AC EURO SIGN :: accord. In one matterâ€”the Esquimault and</t>
-        </is>
-      </c>
+      <c r="K32" s="1" t="inlineStr"/>
       <c r="L32" s="1" t="inlineStr"/>
       <c r="M32" s="1" t="inlineStr"/>
       <c r="N32" s="1" t="inlineStr">
         <is>
-          <t>L1338: isolated marker/symbol line :: 6</t>
+          <t>L1289: isolated marker/symbol line :: E</t>
         </is>
       </c>
       <c r="O32" s="1" t="inlineStr"/>
@@ -2305,16 +2177,12 @@
       <c r="H33" s="1" t="inlineStr"/>
       <c r="I33" s="1" t="inlineStr"/>
       <c r="J33" s="1" t="inlineStr"/>
-      <c r="K33" s="1" t="inlineStr">
-        <is>
-          <t>L819: stray/suspicious non-ASCII glyph(s): U+20AC EURO SIGN, U+FFFD REPLACEMENT CHARACTER :: " people and for the people.â€� Mr. Blake</t>
-        </is>
-      </c>
+      <c r="K33" s="1" t="inlineStr"/>
       <c r="L33" s="1" t="inlineStr"/>
       <c r="M33" s="1" t="inlineStr"/>
       <c r="N33" s="1" t="inlineStr">
         <is>
-          <t>L1362: isolated marker/symbol line :: X</t>
+          <t>L1290: isolated marker/symbol line :: C</t>
         </is>
       </c>
       <c r="O33" s="1" t="inlineStr"/>
@@ -2340,16 +2208,12 @@
       <c r="H34" s="1" t="inlineStr"/>
       <c r="I34" s="1" t="inlineStr"/>
       <c r="J34" s="1" t="inlineStr"/>
-      <c r="K34" s="1" t="inlineStr">
-        <is>
-          <t>L836: stray/suspicious non-ASCII glyph(s): U+20AC EURO SIGN, U+2122 TRADE MARK SIGN :: do so also intelligently. Mr. Blakeâ€™s speech</t>
-        </is>
-      </c>
+      <c r="K34" s="1" t="inlineStr"/>
       <c r="L34" s="1" t="inlineStr"/>
       <c r="M34" s="1" t="inlineStr"/>
       <c r="N34" s="1" t="inlineStr">
         <is>
-          <t>L1363: isolated marker/symbol line :: 3</t>
+          <t>L1291: isolated marker/symbol line :: W</t>
         </is>
       </c>
       <c r="O34" s="1" t="inlineStr"/>
@@ -2375,16 +2239,12 @@
       <c r="H35" s="1" t="inlineStr"/>
       <c r="I35" s="1" t="inlineStr"/>
       <c r="J35" s="1" t="inlineStr"/>
-      <c r="K35" s="1" t="inlineStr">
-        <is>
-          <t>L838: stray/suspicious non-ASCII glyph(s): U+20AC EURO SIGN, U+FFFD REPLACEMENT CHARACTER :: ness, specious argument or â€œclap-trap,â€� and</t>
-        </is>
-      </c>
+      <c r="K35" s="1" t="inlineStr"/>
       <c r="L35" s="1" t="inlineStr"/>
       <c r="M35" s="1" t="inlineStr"/>
       <c r="N35" s="1" t="inlineStr">
         <is>
-          <t>L1460: stray/suspicious non-ASCII glyph(s): U+20AC EURO SIGN | isolated marker/symbol line :: ã€‚</t>
+          <t>L1337: isolated marker/symbol line :: s</t>
         </is>
       </c>
       <c r="O35" s="1" t="inlineStr"/>
@@ -2410,16 +2270,12 @@
       <c r="H36" s="1" t="inlineStr"/>
       <c r="I36" s="1" t="inlineStr"/>
       <c r="J36" s="1" t="inlineStr"/>
-      <c r="K36" s="1" t="inlineStr">
-        <is>
-          <t>L843: stray/suspicious non-ASCII glyph(s): U+20AC EURO SIGN :: act of diplomacyâ€”an achieement of the</t>
-        </is>
-      </c>
+      <c r="K36" s="1" t="inlineStr"/>
       <c r="L36" s="1" t="inlineStr"/>
       <c r="M36" s="1" t="inlineStr"/>
       <c r="N36" s="1" t="inlineStr">
         <is>
-          <t>L1547: isolated marker/symbol line :: a</t>
+          <t>L1338: isolated marker/symbol line :: 6</t>
         </is>
       </c>
       <c r="O36" s="1" t="inlineStr"/>
@@ -2445,16 +2301,12 @@
       <c r="H37" s="1" t="inlineStr"/>
       <c r="I37" s="1" t="inlineStr"/>
       <c r="J37" s="1" t="inlineStr"/>
-      <c r="K37" s="1" t="inlineStr">
-        <is>
-          <t>L844: stray/suspicious non-ASCII glyph(s): U+20AC EURO SIGN :: present Governmentâ€”to whim he might re-</t>
-        </is>
-      </c>
+      <c r="K37" s="1" t="inlineStr"/>
       <c r="L37" s="1" t="inlineStr"/>
       <c r="M37" s="1" t="inlineStr"/>
       <c r="N37" s="1" t="inlineStr">
         <is>
-          <t>L1689: isolated marker/symbol line :: .</t>
+          <t>L1362: isolated marker/symbol line :: X</t>
         </is>
       </c>
       <c r="O37" s="1" t="inlineStr"/>
@@ -2480,16 +2332,12 @@
       <c r="H38" s="1" t="inlineStr"/>
       <c r="I38" s="1" t="inlineStr"/>
       <c r="J38" s="1" t="inlineStr"/>
-      <c r="K38" s="1" t="inlineStr">
-        <is>
-          <t>L880: stray/suspicious non-ASCII glyph(s): U+20AC EURO SIGN, U+2122 TRADE MARK SIGN :: the peopleâ€™s representatives in Parliament as-</t>
-        </is>
-      </c>
+      <c r="K38" s="1" t="inlineStr"/>
       <c r="L38" s="1" t="inlineStr"/>
       <c r="M38" s="1" t="inlineStr"/>
       <c r="N38" s="1" t="inlineStr">
         <is>
-          <t>L1822: isolated marker/symbol line | punctuation artifact: hyphen/bullet debris :: -**</t>
+          <t>L1363: isolated marker/symbol line :: 3</t>
         </is>
       </c>
       <c r="O38" s="1" t="inlineStr"/>
@@ -2515,16 +2363,12 @@
       <c r="H39" s="1" t="inlineStr"/>
       <c r="I39" s="1" t="inlineStr"/>
       <c r="J39" s="1" t="inlineStr"/>
-      <c r="K39" s="1" t="inlineStr">
-        <is>
-          <t>L902: stray/suspicious non-ASCII glyph(s): U+20AC EURO SIGN :: affairs of the countryâ€”the control over all</t>
-        </is>
-      </c>
+      <c r="K39" s="1" t="inlineStr"/>
       <c r="L39" s="1" t="inlineStr"/>
       <c r="M39" s="1" t="inlineStr"/>
       <c r="N39" s="1" t="inlineStr">
         <is>
-          <t>L1829: stray/suspicious non-ASCII glyph(s): U+20AC EURO SIGN | isolated marker/symbol line :: ã€‚</t>
+          <t>L1460: stray/suspicious non-ASCII glyph(s): U+3002 IDEOGRAPHIC FULL STOP | isolated marker/symbol line :: 。</t>
         </is>
       </c>
       <c r="O39" s="1" t="inlineStr"/>
@@ -2550,16 +2394,12 @@
       <c r="H40" s="1" t="inlineStr"/>
       <c r="I40" s="1" t="inlineStr"/>
       <c r="J40" s="1" t="inlineStr"/>
-      <c r="K40" s="1" t="inlineStr">
-        <is>
-          <t>L934: stray/suspicious non-ASCII glyph(s): U+20AC EURO SIGN :: LYNDEN.â€” The Vocal and Instrumental</t>
-        </is>
-      </c>
+      <c r="K40" s="1" t="inlineStr"/>
       <c r="L40" s="1" t="inlineStr"/>
       <c r="M40" s="1" t="inlineStr"/>
       <c r="N40" s="1" t="inlineStr">
         <is>
-          <t>L1855: isolated marker/symbol line :: y</t>
+          <t>L1547: isolated marker/symbol line :: a</t>
         </is>
       </c>
       <c r="O40" s="1" t="inlineStr"/>
@@ -2585,16 +2425,12 @@
       <c r="H41" s="1" t="inlineStr"/>
       <c r="I41" s="1" t="inlineStr"/>
       <c r="J41" s="1" t="inlineStr"/>
-      <c r="K41" s="1" t="inlineStr">
-        <is>
-          <t>L982: stray/suspicious non-ASCII glyph(s): U+20AC EURO SIGN :: â€” REPLY.</t>
-        </is>
-      </c>
+      <c r="K41" s="1" t="inlineStr"/>
       <c r="L41" s="1" t="inlineStr"/>
       <c r="M41" s="1" t="inlineStr"/>
       <c r="N41" s="1" t="inlineStr">
         <is>
-          <t>L1856: isolated marker/symbol line :: b</t>
+          <t>L1689: isolated marker/symbol line :: .</t>
         </is>
       </c>
       <c r="O41" s="1" t="inlineStr"/>
@@ -2620,16 +2456,12 @@
       <c r="H42" s="1" t="inlineStr"/>
       <c r="I42" s="1" t="inlineStr"/>
       <c r="J42" s="1" t="inlineStr"/>
-      <c r="K42" s="1" t="inlineStr">
-        <is>
-          <t>L984: stray/suspicious non-ASCII glyph(s): U+20AC EURO SIGN :: MR. CHAIRMAN, LADIES AND GENTLEMEN,â€”I</t>
-        </is>
-      </c>
+      <c r="K42" s="1" t="inlineStr"/>
       <c r="L42" s="1" t="inlineStr"/>
       <c r="M42" s="1" t="inlineStr"/>
       <c r="N42" s="1" t="inlineStr">
         <is>
-          <t>L1904: isolated marker/symbol line :: -</t>
+          <t>L1822: isolated marker/symbol line | punctuation artifact: hyphen/bullet debris :: -**</t>
         </is>
       </c>
       <c r="O42" s="1" t="inlineStr"/>
@@ -2655,16 +2487,12 @@
       <c r="H43" s="1" t="inlineStr"/>
       <c r="I43" s="1" t="inlineStr"/>
       <c r="J43" s="1" t="inlineStr"/>
-      <c r="K43" s="1" t="inlineStr">
-        <is>
-          <t>L1036: stray/suspicious non-ASCII glyph(s): U+20AC EURO SIGN :: THE BEACH ROAD.â€”The Saltfleet Township</t>
-        </is>
-      </c>
+      <c r="K43" s="1" t="inlineStr"/>
       <c r="L43" s="1" t="inlineStr"/>
       <c r="M43" s="1" t="inlineStr"/>
       <c r="N43" s="1" t="inlineStr">
         <is>
-          <t>L1943: isolated marker/symbol line :: E</t>
+          <t>L1829: stray/suspicious non-ASCII glyph(s): U+3002 IDEOGRAPHIC FULL STOP | isolated marker/symbol line :: 。</t>
         </is>
       </c>
       <c r="O43" s="1" t="inlineStr"/>
@@ -2690,16 +2518,12 @@
       <c r="H44" s="1" t="inlineStr"/>
       <c r="I44" s="1" t="inlineStr"/>
       <c r="J44" s="1" t="inlineStr"/>
-      <c r="K44" s="1" t="inlineStr">
-        <is>
-          <t>L1209: stray/suspicious non-ASCII glyph(s): U+20AC EURO SIGN :: about 8,000 words â€” counting as district</t>
-        </is>
-      </c>
+      <c r="K44" s="1" t="inlineStr"/>
       <c r="L44" s="1" t="inlineStr"/>
       <c r="M44" s="1" t="inlineStr"/>
       <c r="N44" s="1" t="inlineStr">
         <is>
-          <t>L1958: isolated marker/symbol line :: 1</t>
+          <t>L1855: isolated marker/symbol line :: y</t>
         </is>
       </c>
       <c r="O44" s="1" t="inlineStr"/>
@@ -2725,16 +2549,12 @@
       <c r="H45" s="1" t="inlineStr"/>
       <c r="I45" s="1" t="inlineStr"/>
       <c r="J45" s="1" t="inlineStr"/>
-      <c r="K45" s="1" t="inlineStr">
-        <is>
-          <t>L1212: stray/suspicious non-ASCII glyph(s): U+20AC EURO SIGN, U+2122 TRADE MARK SIGN :: Shakspeareâ€™s vocabulary, estimated on the</t>
-        </is>
-      </c>
+      <c r="K45" s="1" t="inlineStr"/>
       <c r="L45" s="1" t="inlineStr"/>
       <c r="M45" s="1" t="inlineStr"/>
       <c r="N45" s="1" t="inlineStr">
         <is>
-          <t>L2026: isolated marker/symbol line :: 2</t>
+          <t>L1856: isolated marker/symbol line :: b</t>
         </is>
       </c>
       <c r="O45" s="1" t="inlineStr"/>
@@ -2760,16 +2580,12 @@
       <c r="H46" s="1" t="inlineStr"/>
       <c r="I46" s="1" t="inlineStr"/>
       <c r="J46" s="1" t="inlineStr"/>
-      <c r="K46" s="1" t="inlineStr">
-        <is>
-          <t>L1214: stray/suspicious non-ASCII glyph(s): U+20AC EURO SIGN, U+2122 TRADE MARK SIGN :: number, as compared with Miltonâ€™s, which</t>
-        </is>
-      </c>
+      <c r="K46" s="1" t="inlineStr"/>
       <c r="L46" s="1" t="inlineStr"/>
       <c r="M46" s="1" t="inlineStr"/>
       <c r="N46" s="1" t="inlineStr">
         <is>
-          <t>L2027: isolated marker/symbol line :: 0</t>
+          <t>L1904: isolated marker/symbol line :: -</t>
         </is>
       </c>
       <c r="O46" s="1" t="inlineStr"/>
@@ -2795,16 +2611,12 @@
       <c r="H47" s="1" t="inlineStr"/>
       <c r="I47" s="1" t="inlineStr"/>
       <c r="J47" s="1" t="inlineStr"/>
-      <c r="K47" s="1" t="inlineStr">
-        <is>
-          <t>L1218: stray/suspicious non-ASCII glyph(s): U+20AC EURO SIGN, U+2122 TRADE MARK SIGN :: dramatistâ€™s imagination moved.</t>
-        </is>
-      </c>
+      <c r="K47" s="1" t="inlineStr"/>
       <c r="L47" s="1" t="inlineStr"/>
       <c r="M47" s="1" t="inlineStr"/>
       <c r="N47" s="1" t="inlineStr">
         <is>
-          <t>L2028: isolated marker/symbol line :: 6</t>
+          <t>L1943: isolated marker/symbol line :: E</t>
         </is>
       </c>
       <c r="O47" s="1" t="inlineStr"/>
@@ -2830,16 +2642,12 @@
       <c r="H48" s="1" t="inlineStr"/>
       <c r="I48" s="1" t="inlineStr"/>
       <c r="J48" s="1" t="inlineStr"/>
-      <c r="K48" s="1" t="inlineStr">
-        <is>
-          <t>L1226: stray/suspicious non-ASCII glyph(s): U+20AC EURO SIGN :: â€”that is about 6,000 words out of the total</t>
-        </is>
-      </c>
+      <c r="K48" s="1" t="inlineStr"/>
       <c r="L48" s="1" t="inlineStr"/>
       <c r="M48" s="1" t="inlineStr"/>
       <c r="N48" s="1" t="inlineStr">
         <is>
-          <t>L2029: isolated marker/symbol line :: â†’</t>
+          <t>L1958: isolated marker/symbol line :: 1</t>
         </is>
       </c>
       <c r="O48" s="1" t="inlineStr"/>
@@ -2865,16 +2673,12 @@
       <c r="H49" s="1" t="inlineStr"/>
       <c r="I49" s="1" t="inlineStr"/>
       <c r="J49" s="1" t="inlineStr"/>
-      <c r="K49" s="1" t="inlineStr">
-        <is>
-          <t>L1227: stray/suspicious non-ASCII glyph(s): U+20AC EURO SIGN :: 15,000 are not of old English stockâ€”a pro-</t>
-        </is>
-      </c>
+      <c r="K49" s="1" t="inlineStr"/>
       <c r="L49" s="1" t="inlineStr"/>
       <c r="M49" s="1" t="inlineStr"/>
       <c r="N49" s="1" t="inlineStr">
         <is>
-          <t>L2030: isolated marker/symbol line :: 9</t>
+          <t>L2026: isolated marker/symbol line :: 2</t>
         </is>
       </c>
       <c r="O49" s="1" t="inlineStr"/>
@@ -2900,14 +2704,14 @@
       <c r="H50" s="1" t="inlineStr"/>
       <c r="I50" s="1" t="inlineStr"/>
       <c r="J50" s="1" t="inlineStr"/>
-      <c r="K50" s="1" t="inlineStr">
-        <is>
-          <t>L1232: stray/suspicious non-ASCII glyph(s): U+20AC EURO SIGN :: non-English element is about two-thirdsâ€”</t>
-        </is>
-      </c>
+      <c r="K50" s="1" t="inlineStr"/>
       <c r="L50" s="1" t="inlineStr"/>
       <c r="M50" s="1" t="inlineStr"/>
-      <c r="N50" s="1" t="inlineStr"/>
+      <c r="N50" s="1" t="inlineStr">
+        <is>
+          <t>L2027: isolated marker/symbol line :: 0</t>
+        </is>
+      </c>
       <c r="O50" s="1" t="inlineStr"/>
       <c r="P50" s="1" t="inlineStr"/>
       <c r="Q50" s="1" t="inlineStr"/>
@@ -2931,14 +2735,14 @@
       <c r="H51" s="1" t="inlineStr"/>
       <c r="I51" s="1" t="inlineStr"/>
       <c r="J51" s="1" t="inlineStr"/>
-      <c r="K51" s="1" t="inlineStr">
-        <is>
-          <t>L1235: stray/suspicious non-ASCII glyph(s): U+20AC EURO SIGN, U+2122 TRADE MARK SIGN :: A word belongs to a writerâ€™s vocabulary if he</t>
-        </is>
-      </c>
+      <c r="K51" s="1" t="inlineStr"/>
       <c r="L51" s="1" t="inlineStr"/>
       <c r="M51" s="1" t="inlineStr"/>
-      <c r="N51" s="1" t="inlineStr"/>
+      <c r="N51" s="1" t="inlineStr">
+        <is>
+          <t>L2028: isolated marker/symbol line :: 6</t>
+        </is>
+      </c>
       <c r="O51" s="1" t="inlineStr"/>
       <c r="P51" s="1" t="inlineStr"/>
       <c r="Q51" s="1" t="inlineStr"/>
@@ -2962,14 +2766,14 @@
       <c r="H52" s="1" t="inlineStr"/>
       <c r="I52" s="1" t="inlineStr"/>
       <c r="J52" s="1" t="inlineStr"/>
-      <c r="K52" s="1" t="inlineStr">
-        <is>
-          <t>L1288: stray/suspicious non-ASCII glyph(s): U+20AC EURO SIGN :: SECONDS.â€”On Sunday, Feb. 28, the pneuma-</t>
-        </is>
-      </c>
+      <c r="K52" s="1" t="inlineStr"/>
       <c r="L52" s="1" t="inlineStr"/>
       <c r="M52" s="1" t="inlineStr"/>
-      <c r="N52" s="1" t="inlineStr"/>
+      <c r="N52" s="1" t="inlineStr">
+        <is>
+          <t>L2029: stray/suspicious non-ASCII glyph(s): U+2192 RIGHTWARDS ARROW | isolated marker/symbol line :: →</t>
+        </is>
+      </c>
       <c r="O52" s="1" t="inlineStr"/>
       <c r="P52" s="1" t="inlineStr"/>
       <c r="Q52" s="1" t="inlineStr"/>
@@ -2993,14 +2797,14 @@
       <c r="H53" s="1" t="inlineStr"/>
       <c r="I53" s="1" t="inlineStr"/>
       <c r="J53" s="1" t="inlineStr"/>
-      <c r="K53" s="1" t="inlineStr">
-        <is>
-          <t>L1294: stray/suspicious non-ASCII glyph(s): U+20AC EURO SIGN :: be sent from one end of the city to anotherâ€”a</t>
-        </is>
-      </c>
+      <c r="K53" s="1" t="inlineStr"/>
       <c r="L53" s="1" t="inlineStr"/>
       <c r="M53" s="1" t="inlineStr"/>
-      <c r="N53" s="1" t="inlineStr"/>
+      <c r="N53" s="1" t="inlineStr">
+        <is>
+          <t>L2030: isolated marker/symbol line :: 9</t>
+        </is>
+      </c>
       <c r="O53" s="1" t="inlineStr"/>
       <c r="P53" s="1" t="inlineStr"/>
       <c r="Q53" s="1" t="inlineStr"/>
@@ -3013,1928 +2817,6 @@
       <c r="X53" s="1" t="inlineStr"/>
       <c r="Y53" s="1" t="inlineStr"/>
     </row>
-    <row r="54">
-      <c r="A54" s="1" t="inlineStr"/>
-      <c r="B54" s="1" t="inlineStr"/>
-      <c r="C54" s="1" t="inlineStr"/>
-      <c r="D54" s="1" t="inlineStr"/>
-      <c r="E54" s="1" t="inlineStr"/>
-      <c r="F54" s="1" t="inlineStr"/>
-      <c r="G54" s="1" t="inlineStr"/>
-      <c r="H54" s="1" t="inlineStr"/>
-      <c r="I54" s="1" t="inlineStr"/>
-      <c r="J54" s="1" t="inlineStr"/>
-      <c r="K54" s="1" t="inlineStr">
-        <is>
-          <t>L1295: stray/suspicious non-ASCII glyph(s): U+20AC EURO SIGN :: distance of about eight milesâ€”in something</t>
-        </is>
-      </c>
-      <c r="L54" s="1" t="inlineStr"/>
-      <c r="M54" s="1" t="inlineStr"/>
-      <c r="N54" s="1" t="inlineStr"/>
-      <c r="O54" s="1" t="inlineStr"/>
-      <c r="P54" s="1" t="inlineStr"/>
-      <c r="Q54" s="1" t="inlineStr"/>
-      <c r="R54" s="1" t="inlineStr"/>
-      <c r="S54" s="1" t="inlineStr"/>
-      <c r="T54" s="1" t="inlineStr"/>
-      <c r="U54" s="1" t="inlineStr"/>
-      <c r="V54" s="1" t="inlineStr"/>
-      <c r="W54" s="1" t="inlineStr"/>
-      <c r="X54" s="1" t="inlineStr"/>
-      <c r="Y54" s="1" t="inlineStr"/>
-    </row>
-    <row r="55">
-      <c r="A55" s="1" t="inlineStr"/>
-      <c r="B55" s="1" t="inlineStr"/>
-      <c r="C55" s="1" t="inlineStr"/>
-      <c r="D55" s="1" t="inlineStr"/>
-      <c r="E55" s="1" t="inlineStr"/>
-      <c r="F55" s="1" t="inlineStr"/>
-      <c r="G55" s="1" t="inlineStr"/>
-      <c r="H55" s="1" t="inlineStr"/>
-      <c r="I55" s="1" t="inlineStr"/>
-      <c r="J55" s="1" t="inlineStr"/>
-      <c r="K55" s="1" t="inlineStr">
-        <is>
-          <t>L1339: stray/suspicious non-ASCII glyph(s): U+20AC EURO SIGN :: This is the first instance of a large cityâ€”</t>
-        </is>
-      </c>
-      <c r="L55" s="1" t="inlineStr"/>
-      <c r="M55" s="1" t="inlineStr"/>
-      <c r="N55" s="1" t="inlineStr"/>
-      <c r="O55" s="1" t="inlineStr"/>
-      <c r="P55" s="1" t="inlineStr"/>
-      <c r="Q55" s="1" t="inlineStr"/>
-      <c r="R55" s="1" t="inlineStr"/>
-      <c r="S55" s="1" t="inlineStr"/>
-      <c r="T55" s="1" t="inlineStr"/>
-      <c r="U55" s="1" t="inlineStr"/>
-      <c r="V55" s="1" t="inlineStr"/>
-      <c r="W55" s="1" t="inlineStr"/>
-      <c r="X55" s="1" t="inlineStr"/>
-      <c r="Y55" s="1" t="inlineStr"/>
-    </row>
-    <row r="56">
-      <c r="A56" s="1" t="inlineStr"/>
-      <c r="B56" s="1" t="inlineStr"/>
-      <c r="C56" s="1" t="inlineStr"/>
-      <c r="D56" s="1" t="inlineStr"/>
-      <c r="E56" s="1" t="inlineStr"/>
-      <c r="F56" s="1" t="inlineStr"/>
-      <c r="G56" s="1" t="inlineStr"/>
-      <c r="H56" s="1" t="inlineStr"/>
-      <c r="I56" s="1" t="inlineStr"/>
-      <c r="J56" s="1" t="inlineStr"/>
-      <c r="K56" s="1" t="inlineStr">
-        <is>
-          <t>L1340: stray/suspicious non-ASCII glyph(s): U+20AC EURO SIGN | localized OCR phrase divergence vs other OCR: "0ooinhabitantsgiving" vs "000 inhabitants giving" :: Vienna has about 900,000 inhabitantsâ€”giving</t>
-        </is>
-      </c>
-      <c r="L56" s="1" t="inlineStr"/>
-      <c r="M56" s="1" t="inlineStr"/>
-      <c r="N56" s="1" t="inlineStr"/>
-      <c r="O56" s="1" t="inlineStr"/>
-      <c r="P56" s="1" t="inlineStr"/>
-      <c r="Q56" s="1" t="inlineStr"/>
-      <c r="R56" s="1" t="inlineStr"/>
-      <c r="S56" s="1" t="inlineStr"/>
-      <c r="T56" s="1" t="inlineStr"/>
-      <c r="U56" s="1" t="inlineStr"/>
-      <c r="V56" s="1" t="inlineStr"/>
-      <c r="W56" s="1" t="inlineStr"/>
-      <c r="X56" s="1" t="inlineStr"/>
-      <c r="Y56" s="1" t="inlineStr"/>
-    </row>
-    <row r="57">
-      <c r="A57" s="1" t="inlineStr"/>
-      <c r="B57" s="1" t="inlineStr"/>
-      <c r="C57" s="1" t="inlineStr"/>
-      <c r="D57" s="1" t="inlineStr"/>
-      <c r="E57" s="1" t="inlineStr"/>
-      <c r="F57" s="1" t="inlineStr"/>
-      <c r="G57" s="1" t="inlineStr"/>
-      <c r="H57" s="1" t="inlineStr"/>
-      <c r="I57" s="1" t="inlineStr"/>
-      <c r="J57" s="1" t="inlineStr"/>
-      <c r="K57" s="1" t="inlineStr">
-        <is>
-          <t>L1342: stray/suspicious non-ASCII glyph(s): U+20AC EURO SIGN :: a moderate cost.â€”N. Y. Mercury.</t>
-        </is>
-      </c>
-      <c r="L57" s="1" t="inlineStr"/>
-      <c r="M57" s="1" t="inlineStr"/>
-      <c r="N57" s="1" t="inlineStr"/>
-      <c r="O57" s="1" t="inlineStr"/>
-      <c r="P57" s="1" t="inlineStr"/>
-      <c r="Q57" s="1" t="inlineStr"/>
-      <c r="R57" s="1" t="inlineStr"/>
-      <c r="S57" s="1" t="inlineStr"/>
-      <c r="T57" s="1" t="inlineStr"/>
-      <c r="U57" s="1" t="inlineStr"/>
-      <c r="V57" s="1" t="inlineStr"/>
-      <c r="W57" s="1" t="inlineStr"/>
-      <c r="X57" s="1" t="inlineStr"/>
-      <c r="Y57" s="1" t="inlineStr"/>
-    </row>
-    <row r="58">
-      <c r="A58" s="1" t="inlineStr"/>
-      <c r="B58" s="1" t="inlineStr"/>
-      <c r="C58" s="1" t="inlineStr"/>
-      <c r="D58" s="1" t="inlineStr"/>
-      <c r="E58" s="1" t="inlineStr"/>
-      <c r="F58" s="1" t="inlineStr"/>
-      <c r="G58" s="1" t="inlineStr"/>
-      <c r="H58" s="1" t="inlineStr"/>
-      <c r="I58" s="1" t="inlineStr"/>
-      <c r="J58" s="1" t="inlineStr"/>
-      <c r="K58" s="1" t="inlineStr">
-        <is>
-          <t>L1356: stray/suspicious non-ASCII glyph(s): U+20AC EURO SIGN :: caution by the action of a ratâ€”not indeed a</t>
-        </is>
-      </c>
-      <c r="L58" s="1" t="inlineStr"/>
-      <c r="M58" s="1" t="inlineStr"/>
-      <c r="N58" s="1" t="inlineStr"/>
-      <c r="O58" s="1" t="inlineStr"/>
-      <c r="P58" s="1" t="inlineStr"/>
-      <c r="Q58" s="1" t="inlineStr"/>
-      <c r="R58" s="1" t="inlineStr"/>
-      <c r="S58" s="1" t="inlineStr"/>
-      <c r="T58" s="1" t="inlineStr"/>
-      <c r="U58" s="1" t="inlineStr"/>
-      <c r="V58" s="1" t="inlineStr"/>
-      <c r="W58" s="1" t="inlineStr"/>
-      <c r="X58" s="1" t="inlineStr"/>
-      <c r="Y58" s="1" t="inlineStr"/>
-    </row>
-    <row r="59">
-      <c r="A59" s="1" t="inlineStr"/>
-      <c r="B59" s="1" t="inlineStr"/>
-      <c r="C59" s="1" t="inlineStr"/>
-      <c r="D59" s="1" t="inlineStr"/>
-      <c r="E59" s="1" t="inlineStr"/>
-      <c r="F59" s="1" t="inlineStr"/>
-      <c r="G59" s="1" t="inlineStr"/>
-      <c r="H59" s="1" t="inlineStr"/>
-      <c r="I59" s="1" t="inlineStr"/>
-      <c r="J59" s="1" t="inlineStr"/>
-      <c r="K59" s="1" t="inlineStr">
-        <is>
-          <t>L1358: stray/suspicious non-ASCII glyph(s): U+20AC EURO SIGN :: fide ratâ€”who has declined to follow the course</t>
-        </is>
-      </c>
-      <c r="L59" s="1" t="inlineStr"/>
-      <c r="M59" s="1" t="inlineStr"/>
-      <c r="N59" s="1" t="inlineStr"/>
-      <c r="O59" s="1" t="inlineStr"/>
-      <c r="P59" s="1" t="inlineStr"/>
-      <c r="Q59" s="1" t="inlineStr"/>
-      <c r="R59" s="1" t="inlineStr"/>
-      <c r="S59" s="1" t="inlineStr"/>
-      <c r="T59" s="1" t="inlineStr"/>
-      <c r="U59" s="1" t="inlineStr"/>
-      <c r="V59" s="1" t="inlineStr"/>
-      <c r="W59" s="1" t="inlineStr"/>
-      <c r="X59" s="1" t="inlineStr"/>
-      <c r="Y59" s="1" t="inlineStr"/>
-    </row>
-    <row r="60">
-      <c r="A60" s="1" t="inlineStr"/>
-      <c r="B60" s="1" t="inlineStr"/>
-      <c r="C60" s="1" t="inlineStr"/>
-      <c r="D60" s="1" t="inlineStr"/>
-      <c r="E60" s="1" t="inlineStr"/>
-      <c r="F60" s="1" t="inlineStr"/>
-      <c r="G60" s="1" t="inlineStr"/>
-      <c r="H60" s="1" t="inlineStr"/>
-      <c r="I60" s="1" t="inlineStr"/>
-      <c r="J60" s="1" t="inlineStr"/>
-      <c r="K60" s="1" t="inlineStr">
-        <is>
-          <t>L1422: stray/suspicious non-ASCII glyph(s): U+20AC EURO SIGN :: liamentâ€”to the men who elected the mem-</t>
-        </is>
-      </c>
-      <c r="L60" s="1" t="inlineStr"/>
-      <c r="M60" s="1" t="inlineStr"/>
-      <c r="N60" s="1" t="inlineStr"/>
-      <c r="O60" s="1" t="inlineStr"/>
-      <c r="P60" s="1" t="inlineStr"/>
-      <c r="Q60" s="1" t="inlineStr"/>
-      <c r="R60" s="1" t="inlineStr"/>
-      <c r="S60" s="1" t="inlineStr"/>
-      <c r="T60" s="1" t="inlineStr"/>
-      <c r="U60" s="1" t="inlineStr"/>
-      <c r="V60" s="1" t="inlineStr"/>
-      <c r="W60" s="1" t="inlineStr"/>
-      <c r="X60" s="1" t="inlineStr"/>
-      <c r="Y60" s="1" t="inlineStr"/>
-    </row>
-    <row r="61">
-      <c r="A61" s="1" t="inlineStr"/>
-      <c r="B61" s="1" t="inlineStr"/>
-      <c r="C61" s="1" t="inlineStr"/>
-      <c r="D61" s="1" t="inlineStr"/>
-      <c r="E61" s="1" t="inlineStr"/>
-      <c r="F61" s="1" t="inlineStr"/>
-      <c r="G61" s="1" t="inlineStr"/>
-      <c r="H61" s="1" t="inlineStr"/>
-      <c r="I61" s="1" t="inlineStr"/>
-      <c r="J61" s="1" t="inlineStr"/>
-      <c r="K61" s="1" t="inlineStr">
-        <is>
-          <t>L1423: stray/suspicious non-ASCII glyph(s): U+20AC EURO SIGN :: bers of Parliamentâ€”that he looked for the</t>
-        </is>
-      </c>
-      <c r="L61" s="1" t="inlineStr"/>
-      <c r="M61" s="1" t="inlineStr"/>
-      <c r="N61" s="1" t="inlineStr"/>
-      <c r="O61" s="1" t="inlineStr"/>
-      <c r="P61" s="1" t="inlineStr"/>
-      <c r="Q61" s="1" t="inlineStr"/>
-      <c r="R61" s="1" t="inlineStr"/>
-      <c r="S61" s="1" t="inlineStr"/>
-      <c r="T61" s="1" t="inlineStr"/>
-      <c r="U61" s="1" t="inlineStr"/>
-      <c r="V61" s="1" t="inlineStr"/>
-      <c r="W61" s="1" t="inlineStr"/>
-      <c r="X61" s="1" t="inlineStr"/>
-      <c r="Y61" s="1" t="inlineStr"/>
-    </row>
-    <row r="62">
-      <c r="A62" s="1" t="inlineStr"/>
-      <c r="B62" s="1" t="inlineStr"/>
-      <c r="C62" s="1" t="inlineStr"/>
-      <c r="D62" s="1" t="inlineStr"/>
-      <c r="E62" s="1" t="inlineStr"/>
-      <c r="F62" s="1" t="inlineStr"/>
-      <c r="G62" s="1" t="inlineStr"/>
-      <c r="H62" s="1" t="inlineStr"/>
-      <c r="I62" s="1" t="inlineStr"/>
-      <c r="J62" s="1" t="inlineStr"/>
-      <c r="K62" s="1" t="inlineStr">
-        <is>
-          <t>L1429: stray/suspicious non-ASCII glyph(s): U+20AC EURO SIGN :: elty, passed through three phasesâ€”first they</t>
-        </is>
-      </c>
-      <c r="L62" s="1" t="inlineStr"/>
-      <c r="M62" s="1" t="inlineStr"/>
-      <c r="N62" s="1" t="inlineStr"/>
-      <c r="O62" s="1" t="inlineStr"/>
-      <c r="P62" s="1" t="inlineStr"/>
-      <c r="Q62" s="1" t="inlineStr"/>
-      <c r="R62" s="1" t="inlineStr"/>
-      <c r="S62" s="1" t="inlineStr"/>
-      <c r="T62" s="1" t="inlineStr"/>
-      <c r="U62" s="1" t="inlineStr"/>
-      <c r="V62" s="1" t="inlineStr"/>
-      <c r="W62" s="1" t="inlineStr"/>
-      <c r="X62" s="1" t="inlineStr"/>
-      <c r="Y62" s="1" t="inlineStr"/>
-    </row>
-    <row r="63">
-      <c r="A63" s="1" t="inlineStr"/>
-      <c r="B63" s="1" t="inlineStr"/>
-      <c r="C63" s="1" t="inlineStr"/>
-      <c r="D63" s="1" t="inlineStr"/>
-      <c r="E63" s="1" t="inlineStr"/>
-      <c r="F63" s="1" t="inlineStr"/>
-      <c r="G63" s="1" t="inlineStr"/>
-      <c r="H63" s="1" t="inlineStr"/>
-      <c r="I63" s="1" t="inlineStr"/>
-      <c r="J63" s="1" t="inlineStr"/>
-      <c r="K63" s="1" t="inlineStr">
-        <is>
-          <t>L1441: stray/suspicious non-ASCII glyph(s): U+20AC EURO SIGN :: outâ€”unless of course the progress of opinion</t>
-        </is>
-      </c>
-      <c r="L63" s="1" t="inlineStr"/>
-      <c r="M63" s="1" t="inlineStr"/>
-      <c r="N63" s="1" t="inlineStr"/>
-      <c r="O63" s="1" t="inlineStr"/>
-      <c r="P63" s="1" t="inlineStr"/>
-      <c r="Q63" s="1" t="inlineStr"/>
-      <c r="R63" s="1" t="inlineStr"/>
-      <c r="S63" s="1" t="inlineStr"/>
-      <c r="T63" s="1" t="inlineStr"/>
-      <c r="U63" s="1" t="inlineStr"/>
-      <c r="V63" s="1" t="inlineStr"/>
-      <c r="W63" s="1" t="inlineStr"/>
-      <c r="X63" s="1" t="inlineStr"/>
-      <c r="Y63" s="1" t="inlineStr"/>
-    </row>
-    <row r="64">
-      <c r="A64" s="1" t="inlineStr"/>
-      <c r="B64" s="1" t="inlineStr"/>
-      <c r="C64" s="1" t="inlineStr"/>
-      <c r="D64" s="1" t="inlineStr"/>
-      <c r="E64" s="1" t="inlineStr"/>
-      <c r="F64" s="1" t="inlineStr"/>
-      <c r="G64" s="1" t="inlineStr"/>
-      <c r="H64" s="1" t="inlineStr"/>
-      <c r="I64" s="1" t="inlineStr"/>
-      <c r="J64" s="1" t="inlineStr"/>
-      <c r="K64" s="1" t="inlineStr">
-        <is>
-          <t>L1476: stray/suspicious non-ASCII glyph(s): U+20AC EURO SIGN :: senseâ€”and on some topics of great conse-</t>
-        </is>
-      </c>
-      <c r="L64" s="1" t="inlineStr"/>
-      <c r="M64" s="1" t="inlineStr"/>
-      <c r="N64" s="1" t="inlineStr"/>
-      <c r="O64" s="1" t="inlineStr"/>
-      <c r="P64" s="1" t="inlineStr"/>
-      <c r="Q64" s="1" t="inlineStr"/>
-      <c r="R64" s="1" t="inlineStr"/>
-      <c r="S64" s="1" t="inlineStr"/>
-      <c r="T64" s="1" t="inlineStr"/>
-      <c r="U64" s="1" t="inlineStr"/>
-      <c r="V64" s="1" t="inlineStr"/>
-      <c r="W64" s="1" t="inlineStr"/>
-      <c r="X64" s="1" t="inlineStr"/>
-      <c r="Y64" s="1" t="inlineStr"/>
-    </row>
-    <row r="65">
-      <c r="A65" s="1" t="inlineStr"/>
-      <c r="B65" s="1" t="inlineStr"/>
-      <c r="C65" s="1" t="inlineStr"/>
-      <c r="D65" s="1" t="inlineStr"/>
-      <c r="E65" s="1" t="inlineStr"/>
-      <c r="F65" s="1" t="inlineStr"/>
-      <c r="G65" s="1" t="inlineStr"/>
-      <c r="H65" s="1" t="inlineStr"/>
-      <c r="I65" s="1" t="inlineStr"/>
-      <c r="J65" s="1" t="inlineStr"/>
-      <c r="K65" s="1" t="inlineStr">
-        <is>
-          <t>L1477: stray/suspicious non-ASCII glyph(s): U+20AC EURO SIGN :: quence to ourselvesâ€”less freedom of talk and</t>
-        </is>
-      </c>
-      <c r="L65" s="1" t="inlineStr"/>
-      <c r="M65" s="1" t="inlineStr"/>
-      <c r="N65" s="1" t="inlineStr"/>
-      <c r="O65" s="1" t="inlineStr"/>
-      <c r="P65" s="1" t="inlineStr"/>
-      <c r="Q65" s="1" t="inlineStr"/>
-      <c r="R65" s="1" t="inlineStr"/>
-      <c r="S65" s="1" t="inlineStr"/>
-      <c r="T65" s="1" t="inlineStr"/>
-      <c r="U65" s="1" t="inlineStr"/>
-      <c r="V65" s="1" t="inlineStr"/>
-      <c r="W65" s="1" t="inlineStr"/>
-      <c r="X65" s="1" t="inlineStr"/>
-      <c r="Y65" s="1" t="inlineStr"/>
-    </row>
-    <row r="66">
-      <c r="A66" s="1" t="inlineStr"/>
-      <c r="B66" s="1" t="inlineStr"/>
-      <c r="C66" s="1" t="inlineStr"/>
-      <c r="D66" s="1" t="inlineStr"/>
-      <c r="E66" s="1" t="inlineStr"/>
-      <c r="F66" s="1" t="inlineStr"/>
-      <c r="G66" s="1" t="inlineStr"/>
-      <c r="H66" s="1" t="inlineStr"/>
-      <c r="I66" s="1" t="inlineStr"/>
-      <c r="J66" s="1" t="inlineStr"/>
-      <c r="K66" s="1" t="inlineStr">
-        <is>
-          <t>L1479: stray/suspicious non-ASCII glyph(s): U+00A9 COPYRIGHT SIGN :: land. In dÃ©mocraties Canada they found</t>
-        </is>
-      </c>
-      <c r="L66" s="1" t="inlineStr"/>
-      <c r="M66" s="1" t="inlineStr"/>
-      <c r="N66" s="1" t="inlineStr"/>
-      <c r="O66" s="1" t="inlineStr"/>
-      <c r="P66" s="1" t="inlineStr"/>
-      <c r="Q66" s="1" t="inlineStr"/>
-      <c r="R66" s="1" t="inlineStr"/>
-      <c r="S66" s="1" t="inlineStr"/>
-      <c r="T66" s="1" t="inlineStr"/>
-      <c r="U66" s="1" t="inlineStr"/>
-      <c r="V66" s="1" t="inlineStr"/>
-      <c r="W66" s="1" t="inlineStr"/>
-      <c r="X66" s="1" t="inlineStr"/>
-      <c r="Y66" s="1" t="inlineStr"/>
-    </row>
-    <row r="67">
-      <c r="A67" s="1" t="inlineStr"/>
-      <c r="B67" s="1" t="inlineStr"/>
-      <c r="C67" s="1" t="inlineStr"/>
-      <c r="D67" s="1" t="inlineStr"/>
-      <c r="E67" s="1" t="inlineStr"/>
-      <c r="F67" s="1" t="inlineStr"/>
-      <c r="G67" s="1" t="inlineStr"/>
-      <c r="H67" s="1" t="inlineStr"/>
-      <c r="I67" s="1" t="inlineStr"/>
-      <c r="J67" s="1" t="inlineStr"/>
-      <c r="K67" s="1" t="inlineStr">
-        <is>
-          <t>L1496: stray/suspicious non-ASCII glyph(s): U+20AC EURO SIGN :: tunitiesâ€”rarer though they Would be, no</t>
-        </is>
-      </c>
-      <c r="L67" s="1" t="inlineStr"/>
-      <c r="M67" s="1" t="inlineStr"/>
-      <c r="N67" s="1" t="inlineStr"/>
-      <c r="O67" s="1" t="inlineStr"/>
-      <c r="P67" s="1" t="inlineStr"/>
-      <c r="Q67" s="1" t="inlineStr"/>
-      <c r="R67" s="1" t="inlineStr"/>
-      <c r="S67" s="1" t="inlineStr"/>
-      <c r="T67" s="1" t="inlineStr"/>
-      <c r="U67" s="1" t="inlineStr"/>
-      <c r="V67" s="1" t="inlineStr"/>
-      <c r="W67" s="1" t="inlineStr"/>
-      <c r="X67" s="1" t="inlineStr"/>
-      <c r="Y67" s="1" t="inlineStr"/>
-    </row>
-    <row r="68">
-      <c r="A68" s="1" t="inlineStr"/>
-      <c r="B68" s="1" t="inlineStr"/>
-      <c r="C68" s="1" t="inlineStr"/>
-      <c r="D68" s="1" t="inlineStr"/>
-      <c r="E68" s="1" t="inlineStr"/>
-      <c r="F68" s="1" t="inlineStr"/>
-      <c r="G68" s="1" t="inlineStr"/>
-      <c r="H68" s="1" t="inlineStr"/>
-      <c r="I68" s="1" t="inlineStr"/>
-      <c r="J68" s="1" t="inlineStr"/>
-      <c r="K68" s="1" t="inlineStr">
-        <is>
-          <t>L1497: stray/suspicious non-ASCII glyph(s): U+20AC EURO SIGN :: doubt, than he had had heretoforeâ€”to deve-</t>
-        </is>
-      </c>
-      <c r="L68" s="1" t="inlineStr"/>
-      <c r="M68" s="1" t="inlineStr"/>
-      <c r="N68" s="1" t="inlineStr"/>
-      <c r="O68" s="1" t="inlineStr"/>
-      <c r="P68" s="1" t="inlineStr"/>
-      <c r="Q68" s="1" t="inlineStr"/>
-      <c r="R68" s="1" t="inlineStr"/>
-      <c r="S68" s="1" t="inlineStr"/>
-      <c r="T68" s="1" t="inlineStr"/>
-      <c r="U68" s="1" t="inlineStr"/>
-      <c r="V68" s="1" t="inlineStr"/>
-      <c r="W68" s="1" t="inlineStr"/>
-      <c r="X68" s="1" t="inlineStr"/>
-      <c r="Y68" s="1" t="inlineStr"/>
-    </row>
-    <row r="69">
-      <c r="A69" s="1" t="inlineStr"/>
-      <c r="B69" s="1" t="inlineStr"/>
-      <c r="C69" s="1" t="inlineStr"/>
-      <c r="D69" s="1" t="inlineStr"/>
-      <c r="E69" s="1" t="inlineStr"/>
-      <c r="F69" s="1" t="inlineStr"/>
-      <c r="G69" s="1" t="inlineStr"/>
-      <c r="H69" s="1" t="inlineStr"/>
-      <c r="I69" s="1" t="inlineStr"/>
-      <c r="J69" s="1" t="inlineStr"/>
-      <c r="K69" s="1" t="inlineStr">
-        <is>
-          <t>L1508: stray/suspicious non-ASCII glyph(s): U+20AC EURO SIGN :: upon some of these topicsâ€”each, if dis-</t>
-        </is>
-      </c>
-      <c r="L69" s="1" t="inlineStr"/>
-      <c r="M69" s="1" t="inlineStr"/>
-      <c r="N69" s="1" t="inlineStr"/>
-      <c r="O69" s="1" t="inlineStr"/>
-      <c r="P69" s="1" t="inlineStr"/>
-      <c r="Q69" s="1" t="inlineStr"/>
-      <c r="R69" s="1" t="inlineStr"/>
-      <c r="S69" s="1" t="inlineStr"/>
-      <c r="T69" s="1" t="inlineStr"/>
-      <c r="U69" s="1" t="inlineStr"/>
-      <c r="V69" s="1" t="inlineStr"/>
-      <c r="W69" s="1" t="inlineStr"/>
-      <c r="X69" s="1" t="inlineStr"/>
-      <c r="Y69" s="1" t="inlineStr"/>
-    </row>
-    <row r="70">
-      <c r="A70" s="1" t="inlineStr"/>
-      <c r="B70" s="1" t="inlineStr"/>
-      <c r="C70" s="1" t="inlineStr"/>
-      <c r="D70" s="1" t="inlineStr"/>
-      <c r="E70" s="1" t="inlineStr"/>
-      <c r="F70" s="1" t="inlineStr"/>
-      <c r="G70" s="1" t="inlineStr"/>
-      <c r="H70" s="1" t="inlineStr"/>
-      <c r="I70" s="1" t="inlineStr"/>
-      <c r="J70" s="1" t="inlineStr"/>
-      <c r="K70" s="1" t="inlineStr">
-        <is>
-          <t>L1537: stray/suspicious non-ASCII glyph(s): U+20AC EURO SIGN, U+2122 TRADE MARK SIGN :: the test to a writerâ€™s style, speci-</t>
-        </is>
-      </c>
-      <c r="L70" s="1" t="inlineStr"/>
-      <c r="M70" s="1" t="inlineStr"/>
-      <c r="N70" s="1" t="inlineStr"/>
-      <c r="O70" s="1" t="inlineStr"/>
-      <c r="P70" s="1" t="inlineStr"/>
-      <c r="Q70" s="1" t="inlineStr"/>
-      <c r="R70" s="1" t="inlineStr"/>
-      <c r="S70" s="1" t="inlineStr"/>
-      <c r="T70" s="1" t="inlineStr"/>
-      <c r="U70" s="1" t="inlineStr"/>
-      <c r="V70" s="1" t="inlineStr"/>
-      <c r="W70" s="1" t="inlineStr"/>
-      <c r="X70" s="1" t="inlineStr"/>
-      <c r="Y70" s="1" t="inlineStr"/>
-    </row>
-    <row r="71">
-      <c r="A71" s="1" t="inlineStr"/>
-      <c r="B71" s="1" t="inlineStr"/>
-      <c r="C71" s="1" t="inlineStr"/>
-      <c r="D71" s="1" t="inlineStr"/>
-      <c r="E71" s="1" t="inlineStr"/>
-      <c r="F71" s="1" t="inlineStr"/>
-      <c r="G71" s="1" t="inlineStr"/>
-      <c r="H71" s="1" t="inlineStr"/>
-      <c r="I71" s="1" t="inlineStr"/>
-      <c r="J71" s="1" t="inlineStr"/>
-      <c r="K71" s="1" t="inlineStr">
-        <is>
-          <t>L1551: stray/suspicious non-ASCII glyph(s): U+20AC EURO SIGN, U+2122 TRADE MARK SIGN :: Humeâ€™s average rises to 73 per cent., John-</t>
-        </is>
-      </c>
-      <c r="L71" s="1" t="inlineStr"/>
-      <c r="M71" s="1" t="inlineStr"/>
-      <c r="N71" s="1" t="inlineStr"/>
-      <c r="O71" s="1" t="inlineStr"/>
-      <c r="P71" s="1" t="inlineStr"/>
-      <c r="Q71" s="1" t="inlineStr"/>
-      <c r="R71" s="1" t="inlineStr"/>
-      <c r="S71" s="1" t="inlineStr"/>
-      <c r="T71" s="1" t="inlineStr"/>
-      <c r="U71" s="1" t="inlineStr"/>
-      <c r="V71" s="1" t="inlineStr"/>
-      <c r="W71" s="1" t="inlineStr"/>
-      <c r="X71" s="1" t="inlineStr"/>
-      <c r="Y71" s="1" t="inlineStr"/>
-    </row>
-    <row r="72">
-      <c r="A72" s="1" t="inlineStr"/>
-      <c r="B72" s="1" t="inlineStr"/>
-      <c r="C72" s="1" t="inlineStr"/>
-      <c r="D72" s="1" t="inlineStr"/>
-      <c r="E72" s="1" t="inlineStr"/>
-      <c r="F72" s="1" t="inlineStr"/>
-      <c r="G72" s="1" t="inlineStr"/>
-      <c r="H72" s="1" t="inlineStr"/>
-      <c r="I72" s="1" t="inlineStr"/>
-      <c r="J72" s="1" t="inlineStr"/>
-      <c r="K72" s="1" t="inlineStr">
-        <is>
-          <t>L1553: stray/suspicious non-ASCII glyph(s): U+20AC EURO SIGN :: â€”good testing instances, which give results</t>
-        </is>
-      </c>
-      <c r="L72" s="1" t="inlineStr"/>
-      <c r="M72" s="1" t="inlineStr"/>
-      <c r="N72" s="1" t="inlineStr"/>
-      <c r="O72" s="1" t="inlineStr"/>
-      <c r="P72" s="1" t="inlineStr"/>
-      <c r="Q72" s="1" t="inlineStr"/>
-      <c r="R72" s="1" t="inlineStr"/>
-      <c r="S72" s="1" t="inlineStr"/>
-      <c r="T72" s="1" t="inlineStr"/>
-      <c r="U72" s="1" t="inlineStr"/>
-      <c r="V72" s="1" t="inlineStr"/>
-      <c r="W72" s="1" t="inlineStr"/>
-      <c r="X72" s="1" t="inlineStr"/>
-      <c r="Y72" s="1" t="inlineStr"/>
-    </row>
-    <row r="73">
-      <c r="A73" s="1" t="inlineStr"/>
-      <c r="B73" s="1" t="inlineStr"/>
-      <c r="C73" s="1" t="inlineStr"/>
-      <c r="D73" s="1" t="inlineStr"/>
-      <c r="E73" s="1" t="inlineStr"/>
-      <c r="F73" s="1" t="inlineStr"/>
-      <c r="G73" s="1" t="inlineStr"/>
-      <c r="H73" s="1" t="inlineStr"/>
-      <c r="I73" s="1" t="inlineStr"/>
-      <c r="J73" s="1" t="inlineStr"/>
-      <c r="K73" s="1" t="inlineStr">
-        <is>
-          <t>L1559: stray/suspicious non-ASCII glyph(s): U+20AC EURO SIGN | abbreviation/spacing may be garbled :: cent.â€”i.e., only one word' in four is not of</t>
-        </is>
-      </c>
-      <c r="L73" s="1" t="inlineStr"/>
-      <c r="M73" s="1" t="inlineStr"/>
-      <c r="N73" s="1" t="inlineStr"/>
-      <c r="O73" s="1" t="inlineStr"/>
-      <c r="P73" s="1" t="inlineStr"/>
-      <c r="Q73" s="1" t="inlineStr"/>
-      <c r="R73" s="1" t="inlineStr"/>
-      <c r="S73" s="1" t="inlineStr"/>
-      <c r="T73" s="1" t="inlineStr"/>
-      <c r="U73" s="1" t="inlineStr"/>
-      <c r="V73" s="1" t="inlineStr"/>
-      <c r="W73" s="1" t="inlineStr"/>
-      <c r="X73" s="1" t="inlineStr"/>
-      <c r="Y73" s="1" t="inlineStr"/>
-    </row>
-    <row r="74">
-      <c r="A74" s="1" t="inlineStr"/>
-      <c r="B74" s="1" t="inlineStr"/>
-      <c r="C74" s="1" t="inlineStr"/>
-      <c r="D74" s="1" t="inlineStr"/>
-      <c r="E74" s="1" t="inlineStr"/>
-      <c r="F74" s="1" t="inlineStr"/>
-      <c r="G74" s="1" t="inlineStr"/>
-      <c r="H74" s="1" t="inlineStr"/>
-      <c r="I74" s="1" t="inlineStr"/>
-      <c r="J74" s="1" t="inlineStr"/>
-      <c r="K74" s="1" t="inlineStr">
-        <is>
-          <t>L1572: stray/suspicious non-ASCII glyph(s): U+20AC EURO SIGN, U+2122 TRADE MARK SIGN :: Milton'sâ€”computed from 66 Lâ€™Allegro," " Il</t>
-        </is>
-      </c>
-      <c r="L74" s="1" t="inlineStr"/>
-      <c r="M74" s="1" t="inlineStr"/>
-      <c r="N74" s="1" t="inlineStr"/>
-      <c r="O74" s="1" t="inlineStr"/>
-      <c r="P74" s="1" t="inlineStr"/>
-      <c r="Q74" s="1" t="inlineStr"/>
-      <c r="R74" s="1" t="inlineStr"/>
-      <c r="S74" s="1" t="inlineStr"/>
-      <c r="T74" s="1" t="inlineStr"/>
-      <c r="U74" s="1" t="inlineStr"/>
-      <c r="V74" s="1" t="inlineStr"/>
-      <c r="W74" s="1" t="inlineStr"/>
-      <c r="X74" s="1" t="inlineStr"/>
-      <c r="Y74" s="1" t="inlineStr"/>
-    </row>
-    <row r="75">
-      <c r="A75" s="1" t="inlineStr"/>
-      <c r="B75" s="1" t="inlineStr"/>
-      <c r="C75" s="1" t="inlineStr"/>
-      <c r="D75" s="1" t="inlineStr"/>
-      <c r="E75" s="1" t="inlineStr"/>
-      <c r="F75" s="1" t="inlineStr"/>
-      <c r="G75" s="1" t="inlineStr"/>
-      <c r="H75" s="1" t="inlineStr"/>
-      <c r="I75" s="1" t="inlineStr"/>
-      <c r="J75" s="1" t="inlineStr"/>
-      <c r="K75" s="1" t="inlineStr">
-        <is>
-          <t>L1573: stray/suspicious non-ASCII glyph(s): U+20AC EURO SIGN, U+FFFD REPLACEMENT CHARACTER :: Penseeroso,â€� and " Paradise Lost," Book</t>
-        </is>
-      </c>
-      <c r="L75" s="1" t="inlineStr"/>
-      <c r="M75" s="1" t="inlineStr"/>
-      <c r="N75" s="1" t="inlineStr"/>
-      <c r="O75" s="1" t="inlineStr"/>
-      <c r="P75" s="1" t="inlineStr"/>
-      <c r="Q75" s="1" t="inlineStr"/>
-      <c r="R75" s="1" t="inlineStr"/>
-      <c r="S75" s="1" t="inlineStr"/>
-      <c r="T75" s="1" t="inlineStr"/>
-      <c r="U75" s="1" t="inlineStr"/>
-      <c r="V75" s="1" t="inlineStr"/>
-      <c r="W75" s="1" t="inlineStr"/>
-      <c r="X75" s="1" t="inlineStr"/>
-      <c r="Y75" s="1" t="inlineStr"/>
-    </row>
-    <row r="76">
-      <c r="A76" s="1" t="inlineStr"/>
-      <c r="B76" s="1" t="inlineStr"/>
-      <c r="C76" s="1" t="inlineStr"/>
-      <c r="D76" s="1" t="inlineStr"/>
-      <c r="E76" s="1" t="inlineStr"/>
-      <c r="F76" s="1" t="inlineStr"/>
-      <c r="G76" s="1" t="inlineStr"/>
-      <c r="H76" s="1" t="inlineStr"/>
-      <c r="I76" s="1" t="inlineStr"/>
-      <c r="J76" s="1" t="inlineStr"/>
-      <c r="K76" s="1" t="inlineStr">
-        <is>
-          <t>L1574: stray/suspicious non-ASCII glyph(s): U+20AC EURO SIGN :: IV., is on the whole about 85-â€”80 being the</t>
-        </is>
-      </c>
-      <c r="L76" s="1" t="inlineStr"/>
-      <c r="M76" s="1" t="inlineStr"/>
-      <c r="N76" s="1" t="inlineStr"/>
-      <c r="O76" s="1" t="inlineStr"/>
-      <c r="P76" s="1" t="inlineStr"/>
-      <c r="Q76" s="1" t="inlineStr"/>
-      <c r="R76" s="1" t="inlineStr"/>
-      <c r="S76" s="1" t="inlineStr"/>
-      <c r="T76" s="1" t="inlineStr"/>
-      <c r="U76" s="1" t="inlineStr"/>
-      <c r="V76" s="1" t="inlineStr"/>
-      <c r="W76" s="1" t="inlineStr"/>
-      <c r="X76" s="1" t="inlineStr"/>
-      <c r="Y76" s="1" t="inlineStr"/>
-    </row>
-    <row r="77">
-      <c r="A77" s="1" t="inlineStr"/>
-      <c r="B77" s="1" t="inlineStr"/>
-      <c r="C77" s="1" t="inlineStr"/>
-      <c r="D77" s="1" t="inlineStr"/>
-      <c r="E77" s="1" t="inlineStr"/>
-      <c r="F77" s="1" t="inlineStr"/>
-      <c r="G77" s="1" t="inlineStr"/>
-      <c r="H77" s="1" t="inlineStr"/>
-      <c r="I77" s="1" t="inlineStr"/>
-      <c r="J77" s="1" t="inlineStr"/>
-      <c r="K77" s="1" t="inlineStr">
-        <is>
-          <t>L1583: stray/suspicious non-ASCII glyph(s): U+20AC EURO SIGN :: used once only by Shakspeareâ€”namely,</t>
-        </is>
-      </c>
-      <c r="L77" s="1" t="inlineStr"/>
-      <c r="M77" s="1" t="inlineStr"/>
-      <c r="N77" s="1" t="inlineStr"/>
-      <c r="O77" s="1" t="inlineStr"/>
-      <c r="P77" s="1" t="inlineStr"/>
-      <c r="Q77" s="1" t="inlineStr"/>
-      <c r="R77" s="1" t="inlineStr"/>
-      <c r="S77" s="1" t="inlineStr"/>
-      <c r="T77" s="1" t="inlineStr"/>
-      <c r="U77" s="1" t="inlineStr"/>
-      <c r="V77" s="1" t="inlineStr"/>
-      <c r="W77" s="1" t="inlineStr"/>
-      <c r="X77" s="1" t="inlineStr"/>
-      <c r="Y77" s="1" t="inlineStr"/>
-    </row>
-    <row r="78">
-      <c r="A78" s="1" t="inlineStr"/>
-      <c r="B78" s="1" t="inlineStr"/>
-      <c r="C78" s="1" t="inlineStr"/>
-      <c r="D78" s="1" t="inlineStr"/>
-      <c r="E78" s="1" t="inlineStr"/>
-      <c r="F78" s="1" t="inlineStr"/>
-      <c r="G78" s="1" t="inlineStr"/>
-      <c r="H78" s="1" t="inlineStr"/>
-      <c r="I78" s="1" t="inlineStr"/>
-      <c r="J78" s="1" t="inlineStr"/>
-      <c r="K78" s="1" t="inlineStr">
-        <is>
-          <t>L1625: stray/suspicious non-ASCII glyph(s): U+20AC EURO SIGN :: â€œ Well, brother Dick, I am glad to see you</t>
-        </is>
-      </c>
-      <c r="L78" s="1" t="inlineStr"/>
-      <c r="M78" s="1" t="inlineStr"/>
-      <c r="N78" s="1" t="inlineStr"/>
-      <c r="O78" s="1" t="inlineStr"/>
-      <c r="P78" s="1" t="inlineStr"/>
-      <c r="Q78" s="1" t="inlineStr"/>
-      <c r="R78" s="1" t="inlineStr"/>
-      <c r="S78" s="1" t="inlineStr"/>
-      <c r="T78" s="1" t="inlineStr"/>
-      <c r="U78" s="1" t="inlineStr"/>
-      <c r="V78" s="1" t="inlineStr"/>
-      <c r="W78" s="1" t="inlineStr"/>
-      <c r="X78" s="1" t="inlineStr"/>
-      <c r="Y78" s="1" t="inlineStr"/>
-    </row>
-    <row r="79">
-      <c r="A79" s="1" t="inlineStr"/>
-      <c r="B79" s="1" t="inlineStr"/>
-      <c r="C79" s="1" t="inlineStr"/>
-      <c r="D79" s="1" t="inlineStr"/>
-      <c r="E79" s="1" t="inlineStr"/>
-      <c r="F79" s="1" t="inlineStr"/>
-      <c r="G79" s="1" t="inlineStr"/>
-      <c r="H79" s="1" t="inlineStr"/>
-      <c r="I79" s="1" t="inlineStr"/>
-      <c r="J79" s="1" t="inlineStr"/>
-      <c r="K79" s="1" t="inlineStr">
-        <is>
-          <t>L1631: stray/suspicious non-ASCII glyph(s): U+20AC EURO SIGN, U+2122 TRADE MARK SIGN :: Thatâ€™s doing well, my brother!" said Brother</t>
-        </is>
-      </c>
-      <c r="L79" s="1" t="inlineStr"/>
-      <c r="M79" s="1" t="inlineStr"/>
-      <c r="N79" s="1" t="inlineStr"/>
-      <c r="O79" s="1" t="inlineStr"/>
-      <c r="P79" s="1" t="inlineStr"/>
-      <c r="Q79" s="1" t="inlineStr"/>
-      <c r="R79" s="1" t="inlineStr"/>
-      <c r="S79" s="1" t="inlineStr"/>
-      <c r="T79" s="1" t="inlineStr"/>
-      <c r="U79" s="1" t="inlineStr"/>
-      <c r="V79" s="1" t="inlineStr"/>
-      <c r="W79" s="1" t="inlineStr"/>
-      <c r="X79" s="1" t="inlineStr"/>
-      <c r="Y79" s="1" t="inlineStr"/>
-    </row>
-    <row r="80">
-      <c r="A80" s="1" t="inlineStr"/>
-      <c r="B80" s="1" t="inlineStr"/>
-      <c r="C80" s="1" t="inlineStr"/>
-      <c r="D80" s="1" t="inlineStr"/>
-      <c r="E80" s="1" t="inlineStr"/>
-      <c r="F80" s="1" t="inlineStr"/>
-      <c r="G80" s="1" t="inlineStr"/>
-      <c r="H80" s="1" t="inlineStr"/>
-      <c r="I80" s="1" t="inlineStr"/>
-      <c r="J80" s="1" t="inlineStr"/>
-      <c r="K80" s="1" t="inlineStr">
-        <is>
-          <t>L1635: stray/suspicious non-ASCII glyph(s): U+20AC EURO SIGN, U+2122 TRADE MARK SIGN, U+02DC SMALL TILDE :: sigh of relief, " If heâ€™d said ducks, he'd â€˜a â€˜ad</t>
-        </is>
-      </c>
-      <c r="L80" s="1" t="inlineStr"/>
-      <c r="M80" s="1" t="inlineStr"/>
-      <c r="N80" s="1" t="inlineStr"/>
-      <c r="O80" s="1" t="inlineStr"/>
-      <c r="P80" s="1" t="inlineStr"/>
-      <c r="Q80" s="1" t="inlineStr"/>
-      <c r="R80" s="1" t="inlineStr"/>
-      <c r="S80" s="1" t="inlineStr"/>
-      <c r="T80" s="1" t="inlineStr"/>
-      <c r="U80" s="1" t="inlineStr"/>
-      <c r="V80" s="1" t="inlineStr"/>
-      <c r="W80" s="1" t="inlineStr"/>
-      <c r="X80" s="1" t="inlineStr"/>
-      <c r="Y80" s="1" t="inlineStr"/>
-    </row>
-    <row r="81">
-      <c r="A81" s="1" t="inlineStr"/>
-      <c r="B81" s="1" t="inlineStr"/>
-      <c r="C81" s="1" t="inlineStr"/>
-      <c r="D81" s="1" t="inlineStr"/>
-      <c r="E81" s="1" t="inlineStr"/>
-      <c r="F81" s="1" t="inlineStr"/>
-      <c r="G81" s="1" t="inlineStr"/>
-      <c r="H81" s="1" t="inlineStr"/>
-      <c r="I81" s="1" t="inlineStr"/>
-      <c r="J81" s="1" t="inlineStr"/>
-      <c r="K81" s="1" t="inlineStr">
-        <is>
-          <t>L1706: stray/suspicious non-ASCII glyph(s): U+20AC EURO SIGN, U+2122 TRADE MARK SIGN :: ployed in casting at Laidlawâ€™s Foundry, on the</t>
-        </is>
-      </c>
-      <c r="L81" s="1" t="inlineStr"/>
-      <c r="M81" s="1" t="inlineStr"/>
-      <c r="N81" s="1" t="inlineStr"/>
-      <c r="O81" s="1" t="inlineStr"/>
-      <c r="P81" s="1" t="inlineStr"/>
-      <c r="Q81" s="1" t="inlineStr"/>
-      <c r="R81" s="1" t="inlineStr"/>
-      <c r="S81" s="1" t="inlineStr"/>
-      <c r="T81" s="1" t="inlineStr"/>
-      <c r="U81" s="1" t="inlineStr"/>
-      <c r="V81" s="1" t="inlineStr"/>
-      <c r="W81" s="1" t="inlineStr"/>
-      <c r="X81" s="1" t="inlineStr"/>
-      <c r="Y81" s="1" t="inlineStr"/>
-    </row>
-    <row r="82">
-      <c r="A82" s="1" t="inlineStr"/>
-      <c r="B82" s="1" t="inlineStr"/>
-      <c r="C82" s="1" t="inlineStr"/>
-      <c r="D82" s="1" t="inlineStr"/>
-      <c r="E82" s="1" t="inlineStr"/>
-      <c r="F82" s="1" t="inlineStr"/>
-      <c r="G82" s="1" t="inlineStr"/>
-      <c r="H82" s="1" t="inlineStr"/>
-      <c r="I82" s="1" t="inlineStr"/>
-      <c r="J82" s="1" t="inlineStr"/>
-      <c r="K82" s="1" t="inlineStr">
-        <is>
-          <t>L1717: stray/suspicious non-ASCII glyph(s): U+20AC EURO SIGN, U+2122 TRADE MARK SIGN :: Mullinâ€™s, and is, we believe, progressing favor-</t>
-        </is>
-      </c>
-      <c r="L82" s="1" t="inlineStr"/>
-      <c r="M82" s="1" t="inlineStr"/>
-      <c r="N82" s="1" t="inlineStr"/>
-      <c r="O82" s="1" t="inlineStr"/>
-      <c r="P82" s="1" t="inlineStr"/>
-      <c r="Q82" s="1" t="inlineStr"/>
-      <c r="R82" s="1" t="inlineStr"/>
-      <c r="S82" s="1" t="inlineStr"/>
-      <c r="T82" s="1" t="inlineStr"/>
-      <c r="U82" s="1" t="inlineStr"/>
-      <c r="V82" s="1" t="inlineStr"/>
-      <c r="W82" s="1" t="inlineStr"/>
-      <c r="X82" s="1" t="inlineStr"/>
-      <c r="Y82" s="1" t="inlineStr"/>
-    </row>
-    <row r="83">
-      <c r="A83" s="1" t="inlineStr"/>
-      <c r="B83" s="1" t="inlineStr"/>
-      <c r="C83" s="1" t="inlineStr"/>
-      <c r="D83" s="1" t="inlineStr"/>
-      <c r="E83" s="1" t="inlineStr"/>
-      <c r="F83" s="1" t="inlineStr"/>
-      <c r="G83" s="1" t="inlineStr"/>
-      <c r="H83" s="1" t="inlineStr"/>
-      <c r="I83" s="1" t="inlineStr"/>
-      <c r="J83" s="1" t="inlineStr"/>
-      <c r="K83" s="1" t="inlineStr">
-        <is>
-          <t>L1720: stray/suspicious non-ASCII glyph(s): U+20AC EURO SIGN, U+2122 TRADE MARK SIGN :: The GRANGERSâ€™ Picnic.â€”Acacia Grange,</t>
-        </is>
-      </c>
-      <c r="L83" s="1" t="inlineStr"/>
-      <c r="M83" s="1" t="inlineStr"/>
-      <c r="N83" s="1" t="inlineStr"/>
-      <c r="O83" s="1" t="inlineStr"/>
-      <c r="P83" s="1" t="inlineStr"/>
-      <c r="Q83" s="1" t="inlineStr"/>
-      <c r="R83" s="1" t="inlineStr"/>
-      <c r="S83" s="1" t="inlineStr"/>
-      <c r="T83" s="1" t="inlineStr"/>
-      <c r="U83" s="1" t="inlineStr"/>
-      <c r="V83" s="1" t="inlineStr"/>
-      <c r="W83" s="1" t="inlineStr"/>
-      <c r="X83" s="1" t="inlineStr"/>
-      <c r="Y83" s="1" t="inlineStr"/>
-    </row>
-    <row r="84">
-      <c r="A84" s="1" t="inlineStr"/>
-      <c r="B84" s="1" t="inlineStr"/>
-      <c r="C84" s="1" t="inlineStr"/>
-      <c r="D84" s="1" t="inlineStr"/>
-      <c r="E84" s="1" t="inlineStr"/>
-      <c r="F84" s="1" t="inlineStr"/>
-      <c r="G84" s="1" t="inlineStr"/>
-      <c r="H84" s="1" t="inlineStr"/>
-      <c r="I84" s="1" t="inlineStr"/>
-      <c r="J84" s="1" t="inlineStr"/>
-      <c r="K84" s="1" t="inlineStr">
-        <is>
-          <t>L1745: stray/suspicious non-ASCII glyph(s): U+20AC EURO SIGN :: Overseerâ€”Chas. Carpenter.</t>
-        </is>
-      </c>
-      <c r="L84" s="1" t="inlineStr"/>
-      <c r="M84" s="1" t="inlineStr"/>
-      <c r="N84" s="1" t="inlineStr"/>
-      <c r="O84" s="1" t="inlineStr"/>
-      <c r="P84" s="1" t="inlineStr"/>
-      <c r="Q84" s="1" t="inlineStr"/>
-      <c r="R84" s="1" t="inlineStr"/>
-      <c r="S84" s="1" t="inlineStr"/>
-      <c r="T84" s="1" t="inlineStr"/>
-      <c r="U84" s="1" t="inlineStr"/>
-      <c r="V84" s="1" t="inlineStr"/>
-      <c r="W84" s="1" t="inlineStr"/>
-      <c r="X84" s="1" t="inlineStr"/>
-      <c r="Y84" s="1" t="inlineStr"/>
-    </row>
-    <row r="85">
-      <c r="A85" s="1" t="inlineStr"/>
-      <c r="B85" s="1" t="inlineStr"/>
-      <c r="C85" s="1" t="inlineStr"/>
-      <c r="D85" s="1" t="inlineStr"/>
-      <c r="E85" s="1" t="inlineStr"/>
-      <c r="F85" s="1" t="inlineStr"/>
-      <c r="G85" s="1" t="inlineStr"/>
-      <c r="H85" s="1" t="inlineStr"/>
-      <c r="I85" s="1" t="inlineStr"/>
-      <c r="J85" s="1" t="inlineStr"/>
-      <c r="K85" s="1" t="inlineStr">
-        <is>
-          <t>L1746: stray/suspicious non-ASCII glyph(s): U+20AC EURO SIGN :: Chaplainâ€”G. Carpenter.</t>
-        </is>
-      </c>
-      <c r="L85" s="1" t="inlineStr"/>
-      <c r="M85" s="1" t="inlineStr"/>
-      <c r="N85" s="1" t="inlineStr"/>
-      <c r="O85" s="1" t="inlineStr"/>
-      <c r="P85" s="1" t="inlineStr"/>
-      <c r="Q85" s="1" t="inlineStr"/>
-      <c r="R85" s="1" t="inlineStr"/>
-      <c r="S85" s="1" t="inlineStr"/>
-      <c r="T85" s="1" t="inlineStr"/>
-      <c r="U85" s="1" t="inlineStr"/>
-      <c r="V85" s="1" t="inlineStr"/>
-      <c r="W85" s="1" t="inlineStr"/>
-      <c r="X85" s="1" t="inlineStr"/>
-      <c r="Y85" s="1" t="inlineStr"/>
-    </row>
-    <row r="86">
-      <c r="A86" s="1" t="inlineStr"/>
-      <c r="B86" s="1" t="inlineStr"/>
-      <c r="C86" s="1" t="inlineStr"/>
-      <c r="D86" s="1" t="inlineStr"/>
-      <c r="E86" s="1" t="inlineStr"/>
-      <c r="F86" s="1" t="inlineStr"/>
-      <c r="G86" s="1" t="inlineStr"/>
-      <c r="H86" s="1" t="inlineStr"/>
-      <c r="I86" s="1" t="inlineStr"/>
-      <c r="J86" s="1" t="inlineStr"/>
-      <c r="K86" s="1" t="inlineStr">
-        <is>
-          <t>L1750: stray/suspicious non-ASCII glyph(s): U+20AC EURO SIGN :: Assistant Stewardâ€”E. Smith.</t>
-        </is>
-      </c>
-      <c r="L86" s="1" t="inlineStr"/>
-      <c r="M86" s="1" t="inlineStr"/>
-      <c r="N86" s="1" t="inlineStr"/>
-      <c r="O86" s="1" t="inlineStr"/>
-      <c r="P86" s="1" t="inlineStr"/>
-      <c r="Q86" s="1" t="inlineStr"/>
-      <c r="R86" s="1" t="inlineStr"/>
-      <c r="S86" s="1" t="inlineStr"/>
-      <c r="T86" s="1" t="inlineStr"/>
-      <c r="U86" s="1" t="inlineStr"/>
-      <c r="V86" s="1" t="inlineStr"/>
-      <c r="W86" s="1" t="inlineStr"/>
-      <c r="X86" s="1" t="inlineStr"/>
-      <c r="Y86" s="1" t="inlineStr"/>
-    </row>
-    <row r="87">
-      <c r="A87" s="1" t="inlineStr"/>
-      <c r="B87" s="1" t="inlineStr"/>
-      <c r="C87" s="1" t="inlineStr"/>
-      <c r="D87" s="1" t="inlineStr"/>
-      <c r="E87" s="1" t="inlineStr"/>
-      <c r="F87" s="1" t="inlineStr"/>
-      <c r="G87" s="1" t="inlineStr"/>
-      <c r="H87" s="1" t="inlineStr"/>
-      <c r="I87" s="1" t="inlineStr"/>
-      <c r="J87" s="1" t="inlineStr"/>
-      <c r="K87" s="1" t="inlineStr">
-        <is>
-          <t>L1753: stray/suspicious non-ASCII glyph(s): U+20AC EURO SIGN :: Secretaryâ€”F. M. Carpenter.</t>
-        </is>
-      </c>
-      <c r="L87" s="1" t="inlineStr"/>
-      <c r="M87" s="1" t="inlineStr"/>
-      <c r="N87" s="1" t="inlineStr"/>
-      <c r="O87" s="1" t="inlineStr"/>
-      <c r="P87" s="1" t="inlineStr"/>
-      <c r="Q87" s="1" t="inlineStr"/>
-      <c r="R87" s="1" t="inlineStr"/>
-      <c r="S87" s="1" t="inlineStr"/>
-      <c r="T87" s="1" t="inlineStr"/>
-      <c r="U87" s="1" t="inlineStr"/>
-      <c r="V87" s="1" t="inlineStr"/>
-      <c r="W87" s="1" t="inlineStr"/>
-      <c r="X87" s="1" t="inlineStr"/>
-      <c r="Y87" s="1" t="inlineStr"/>
-    </row>
-    <row r="88">
-      <c r="A88" s="1" t="inlineStr"/>
-      <c r="B88" s="1" t="inlineStr"/>
-      <c r="C88" s="1" t="inlineStr"/>
-      <c r="D88" s="1" t="inlineStr"/>
-      <c r="E88" s="1" t="inlineStr"/>
-      <c r="F88" s="1" t="inlineStr"/>
-      <c r="G88" s="1" t="inlineStr"/>
-      <c r="H88" s="1" t="inlineStr"/>
-      <c r="I88" s="1" t="inlineStr"/>
-      <c r="J88" s="1" t="inlineStr"/>
-      <c r="K88" s="1" t="inlineStr">
-        <is>
-          <t>L1755: stray/suspicious non-ASCII glyph(s): U+20AC EURO SIGN :: Treasurerâ€”J. W. Smith.</t>
-        </is>
-      </c>
-      <c r="L88" s="1" t="inlineStr"/>
-      <c r="M88" s="1" t="inlineStr"/>
-      <c r="N88" s="1" t="inlineStr"/>
-      <c r="O88" s="1" t="inlineStr"/>
-      <c r="P88" s="1" t="inlineStr"/>
-      <c r="Q88" s="1" t="inlineStr"/>
-      <c r="R88" s="1" t="inlineStr"/>
-      <c r="S88" s="1" t="inlineStr"/>
-      <c r="T88" s="1" t="inlineStr"/>
-      <c r="U88" s="1" t="inlineStr"/>
-      <c r="V88" s="1" t="inlineStr"/>
-      <c r="W88" s="1" t="inlineStr"/>
-      <c r="X88" s="1" t="inlineStr"/>
-      <c r="Y88" s="1" t="inlineStr"/>
-    </row>
-    <row r="89">
-      <c r="A89" s="1" t="inlineStr"/>
-      <c r="B89" s="1" t="inlineStr"/>
-      <c r="C89" s="1" t="inlineStr"/>
-      <c r="D89" s="1" t="inlineStr"/>
-      <c r="E89" s="1" t="inlineStr"/>
-      <c r="F89" s="1" t="inlineStr"/>
-      <c r="G89" s="1" t="inlineStr"/>
-      <c r="H89" s="1" t="inlineStr"/>
-      <c r="I89" s="1" t="inlineStr"/>
-      <c r="J89" s="1" t="inlineStr"/>
-      <c r="K89" s="1" t="inlineStr">
-        <is>
-          <t>L1757: stray/suspicious non-ASCII glyph(s): U+20AC EURO SIGN :: Gate-keeper â€”H. P. Van Wagner.â€”</t>
-        </is>
-      </c>
-      <c r="L89" s="1" t="inlineStr"/>
-      <c r="M89" s="1" t="inlineStr"/>
-      <c r="N89" s="1" t="inlineStr"/>
-      <c r="O89" s="1" t="inlineStr"/>
-      <c r="P89" s="1" t="inlineStr"/>
-      <c r="Q89" s="1" t="inlineStr"/>
-      <c r="R89" s="1" t="inlineStr"/>
-      <c r="S89" s="1" t="inlineStr"/>
-      <c r="T89" s="1" t="inlineStr"/>
-      <c r="U89" s="1" t="inlineStr"/>
-      <c r="V89" s="1" t="inlineStr"/>
-      <c r="W89" s="1" t="inlineStr"/>
-      <c r="X89" s="1" t="inlineStr"/>
-      <c r="Y89" s="1" t="inlineStr"/>
-    </row>
-    <row r="90">
-      <c r="A90" s="1" t="inlineStr"/>
-      <c r="B90" s="1" t="inlineStr"/>
-      <c r="C90" s="1" t="inlineStr"/>
-      <c r="D90" s="1" t="inlineStr"/>
-      <c r="E90" s="1" t="inlineStr"/>
-      <c r="F90" s="1" t="inlineStr"/>
-      <c r="G90" s="1" t="inlineStr"/>
-      <c r="H90" s="1" t="inlineStr"/>
-      <c r="I90" s="1" t="inlineStr"/>
-      <c r="J90" s="1" t="inlineStr"/>
-      <c r="K90" s="1" t="inlineStr">
-        <is>
-          <t>L1758: stray/suspicious non-ASCII glyph(s): U+20AC EURO SIGN :: Lady Assistant Stewardessâ€”Miss A. Chambers.</t>
-        </is>
-      </c>
-      <c r="L90" s="1" t="inlineStr"/>
-      <c r="M90" s="1" t="inlineStr"/>
-      <c r="N90" s="1" t="inlineStr"/>
-      <c r="O90" s="1" t="inlineStr"/>
-      <c r="P90" s="1" t="inlineStr"/>
-      <c r="Q90" s="1" t="inlineStr"/>
-      <c r="R90" s="1" t="inlineStr"/>
-      <c r="S90" s="1" t="inlineStr"/>
-      <c r="T90" s="1" t="inlineStr"/>
-      <c r="U90" s="1" t="inlineStr"/>
-      <c r="V90" s="1" t="inlineStr"/>
-      <c r="W90" s="1" t="inlineStr"/>
-      <c r="X90" s="1" t="inlineStr"/>
-      <c r="Y90" s="1" t="inlineStr"/>
-    </row>
-    <row r="91">
-      <c r="A91" s="1" t="inlineStr"/>
-      <c r="B91" s="1" t="inlineStr"/>
-      <c r="C91" s="1" t="inlineStr"/>
-      <c r="D91" s="1" t="inlineStr"/>
-      <c r="E91" s="1" t="inlineStr"/>
-      <c r="F91" s="1" t="inlineStr"/>
-      <c r="G91" s="1" t="inlineStr"/>
-      <c r="H91" s="1" t="inlineStr"/>
-      <c r="I91" s="1" t="inlineStr"/>
-      <c r="J91" s="1" t="inlineStr"/>
-      <c r="K91" s="1" t="inlineStr">
-        <is>
-          <t>L1759: stray/suspicious non-ASCII glyph(s): U+20AC EURO SIGN :: Ceresâ€”Miss M. Van Wagner.</t>
-        </is>
-      </c>
-      <c r="L91" s="1" t="inlineStr"/>
-      <c r="M91" s="1" t="inlineStr"/>
-      <c r="N91" s="1" t="inlineStr"/>
-      <c r="O91" s="1" t="inlineStr"/>
-      <c r="P91" s="1" t="inlineStr"/>
-      <c r="Q91" s="1" t="inlineStr"/>
-      <c r="R91" s="1" t="inlineStr"/>
-      <c r="S91" s="1" t="inlineStr"/>
-      <c r="T91" s="1" t="inlineStr"/>
-      <c r="U91" s="1" t="inlineStr"/>
-      <c r="V91" s="1" t="inlineStr"/>
-      <c r="W91" s="1" t="inlineStr"/>
-      <c r="X91" s="1" t="inlineStr"/>
-      <c r="Y91" s="1" t="inlineStr"/>
-    </row>
-    <row r="92">
-      <c r="A92" s="1" t="inlineStr"/>
-      <c r="B92" s="1" t="inlineStr"/>
-      <c r="C92" s="1" t="inlineStr"/>
-      <c r="D92" s="1" t="inlineStr"/>
-      <c r="E92" s="1" t="inlineStr"/>
-      <c r="F92" s="1" t="inlineStr"/>
-      <c r="G92" s="1" t="inlineStr"/>
-      <c r="H92" s="1" t="inlineStr"/>
-      <c r="I92" s="1" t="inlineStr"/>
-      <c r="J92" s="1" t="inlineStr"/>
-      <c r="K92" s="1" t="inlineStr">
-        <is>
-          <t>L1761: stray/suspicious non-ASCII glyph(s): U+20AC EURO SIGN :: Pomoniaâ€”Mrs. J. Lottridge.</t>
-        </is>
-      </c>
-      <c r="L92" s="1" t="inlineStr"/>
-      <c r="M92" s="1" t="inlineStr"/>
-      <c r="N92" s="1" t="inlineStr"/>
-      <c r="O92" s="1" t="inlineStr"/>
-      <c r="P92" s="1" t="inlineStr"/>
-      <c r="Q92" s="1" t="inlineStr"/>
-      <c r="R92" s="1" t="inlineStr"/>
-      <c r="S92" s="1" t="inlineStr"/>
-      <c r="T92" s="1" t="inlineStr"/>
-      <c r="U92" s="1" t="inlineStr"/>
-      <c r="V92" s="1" t="inlineStr"/>
-      <c r="W92" s="1" t="inlineStr"/>
-      <c r="X92" s="1" t="inlineStr"/>
-      <c r="Y92" s="1" t="inlineStr"/>
-    </row>
-    <row r="93">
-      <c r="A93" s="1" t="inlineStr"/>
-      <c r="B93" s="1" t="inlineStr"/>
-      <c r="C93" s="1" t="inlineStr"/>
-      <c r="D93" s="1" t="inlineStr"/>
-      <c r="E93" s="1" t="inlineStr"/>
-      <c r="F93" s="1" t="inlineStr"/>
-      <c r="G93" s="1" t="inlineStr"/>
-      <c r="H93" s="1" t="inlineStr"/>
-      <c r="I93" s="1" t="inlineStr"/>
-      <c r="J93" s="1" t="inlineStr"/>
-      <c r="K93" s="1" t="inlineStr">
-        <is>
-          <t>L1762: stray/suspicious non-ASCII glyph(s): U+20AC EURO SIGN :: Floraâ€”Miss Emma Jones.</t>
-        </is>
-      </c>
-      <c r="L93" s="1" t="inlineStr"/>
-      <c r="M93" s="1" t="inlineStr"/>
-      <c r="N93" s="1" t="inlineStr"/>
-      <c r="O93" s="1" t="inlineStr"/>
-      <c r="P93" s="1" t="inlineStr"/>
-      <c r="Q93" s="1" t="inlineStr"/>
-      <c r="R93" s="1" t="inlineStr"/>
-      <c r="S93" s="1" t="inlineStr"/>
-      <c r="T93" s="1" t="inlineStr"/>
-      <c r="U93" s="1" t="inlineStr"/>
-      <c r="V93" s="1" t="inlineStr"/>
-      <c r="W93" s="1" t="inlineStr"/>
-      <c r="X93" s="1" t="inlineStr"/>
-      <c r="Y93" s="1" t="inlineStr"/>
-    </row>
-    <row r="94">
-      <c r="A94" s="1" t="inlineStr"/>
-      <c r="B94" s="1" t="inlineStr"/>
-      <c r="C94" s="1" t="inlineStr"/>
-      <c r="D94" s="1" t="inlineStr"/>
-      <c r="E94" s="1" t="inlineStr"/>
-      <c r="F94" s="1" t="inlineStr"/>
-      <c r="G94" s="1" t="inlineStr"/>
-      <c r="H94" s="1" t="inlineStr"/>
-      <c r="I94" s="1" t="inlineStr"/>
-      <c r="J94" s="1" t="inlineStr"/>
-      <c r="K94" s="1" t="inlineStr">
-        <is>
-          <t>L1766: stray/suspicious non-ASCII glyph(s): U+20AC EURO SIGN :: LONDON, June 3.â€”The attendance at the</t>
-        </is>
-      </c>
-      <c r="L94" s="1" t="inlineStr"/>
-      <c r="M94" s="1" t="inlineStr"/>
-      <c r="N94" s="1" t="inlineStr"/>
-      <c r="O94" s="1" t="inlineStr"/>
-      <c r="P94" s="1" t="inlineStr"/>
-      <c r="Q94" s="1" t="inlineStr"/>
-      <c r="R94" s="1" t="inlineStr"/>
-      <c r="S94" s="1" t="inlineStr"/>
-      <c r="T94" s="1" t="inlineStr"/>
-      <c r="U94" s="1" t="inlineStr"/>
-      <c r="V94" s="1" t="inlineStr"/>
-      <c r="W94" s="1" t="inlineStr"/>
-      <c r="X94" s="1" t="inlineStr"/>
-      <c r="Y94" s="1" t="inlineStr"/>
-    </row>
-    <row r="95">
-      <c r="A95" s="1" t="inlineStr"/>
-      <c r="B95" s="1" t="inlineStr"/>
-      <c r="C95" s="1" t="inlineStr"/>
-      <c r="D95" s="1" t="inlineStr"/>
-      <c r="E95" s="1" t="inlineStr"/>
-      <c r="F95" s="1" t="inlineStr"/>
-      <c r="G95" s="1" t="inlineStr"/>
-      <c r="H95" s="1" t="inlineStr"/>
-      <c r="I95" s="1" t="inlineStr"/>
-      <c r="J95" s="1" t="inlineStr"/>
-      <c r="K95" s="1" t="inlineStr">
-        <is>
-          <t>L1772: stray/suspicious non-ASCII glyph(s): U+20AC EURO SIGN :: J. H. Boyle, Long John second. The nextâ€”</t>
-        </is>
-      </c>
-      <c r="L95" s="1" t="inlineStr"/>
-      <c r="M95" s="1" t="inlineStr"/>
-      <c r="N95" s="1" t="inlineStr"/>
-      <c r="O95" s="1" t="inlineStr"/>
-      <c r="P95" s="1" t="inlineStr"/>
-      <c r="Q95" s="1" t="inlineStr"/>
-      <c r="R95" s="1" t="inlineStr"/>
-      <c r="S95" s="1" t="inlineStr"/>
-      <c r="T95" s="1" t="inlineStr"/>
-      <c r="U95" s="1" t="inlineStr"/>
-      <c r="V95" s="1" t="inlineStr"/>
-      <c r="W95" s="1" t="inlineStr"/>
-      <c r="X95" s="1" t="inlineStr"/>
-      <c r="Y95" s="1" t="inlineStr"/>
-    </row>
-    <row r="96">
-      <c r="A96" s="1" t="inlineStr"/>
-      <c r="B96" s="1" t="inlineStr"/>
-      <c r="C96" s="1" t="inlineStr"/>
-      <c r="D96" s="1" t="inlineStr"/>
-      <c r="E96" s="1" t="inlineStr"/>
-      <c r="F96" s="1" t="inlineStr"/>
-      <c r="G96" s="1" t="inlineStr"/>
-      <c r="H96" s="1" t="inlineStr"/>
-      <c r="I96" s="1" t="inlineStr"/>
-      <c r="J96" s="1" t="inlineStr"/>
-      <c r="K96" s="1" t="inlineStr">
-        <is>
-          <t>L1806: stray/suspicious non-ASCII glyph(s): U+20AC EURO SIGN, U+2122 TRADE MARK SIGN :: Keep your horse fat ; donâ€™t allow any one</t>
-        </is>
-      </c>
-      <c r="L96" s="1" t="inlineStr"/>
-      <c r="M96" s="1" t="inlineStr"/>
-      <c r="N96" s="1" t="inlineStr"/>
-      <c r="O96" s="1" t="inlineStr"/>
-      <c r="P96" s="1" t="inlineStr"/>
-      <c r="Q96" s="1" t="inlineStr"/>
-      <c r="R96" s="1" t="inlineStr"/>
-      <c r="S96" s="1" t="inlineStr"/>
-      <c r="T96" s="1" t="inlineStr"/>
-      <c r="U96" s="1" t="inlineStr"/>
-      <c r="V96" s="1" t="inlineStr"/>
-      <c r="W96" s="1" t="inlineStr"/>
-      <c r="X96" s="1" t="inlineStr"/>
-      <c r="Y96" s="1" t="inlineStr"/>
-    </row>
-    <row r="97">
-      <c r="A97" s="1" t="inlineStr"/>
-      <c r="B97" s="1" t="inlineStr"/>
-      <c r="C97" s="1" t="inlineStr"/>
-      <c r="D97" s="1" t="inlineStr"/>
-      <c r="E97" s="1" t="inlineStr"/>
-      <c r="F97" s="1" t="inlineStr"/>
-      <c r="G97" s="1" t="inlineStr"/>
-      <c r="H97" s="1" t="inlineStr"/>
-      <c r="I97" s="1" t="inlineStr"/>
-      <c r="J97" s="1" t="inlineStr"/>
-      <c r="K97" s="1" t="inlineStr">
-        <is>
-          <t>L1813: stray/suspicious non-ASCII glyph(s): U+20AC EURO SIGN, U+00A2 CENT SIGN :: halters.â€¢</t>
-        </is>
-      </c>
-      <c r="L97" s="1" t="inlineStr"/>
-      <c r="M97" s="1" t="inlineStr"/>
-      <c r="N97" s="1" t="inlineStr"/>
-      <c r="O97" s="1" t="inlineStr"/>
-      <c r="P97" s="1" t="inlineStr"/>
-      <c r="Q97" s="1" t="inlineStr"/>
-      <c r="R97" s="1" t="inlineStr"/>
-      <c r="S97" s="1" t="inlineStr"/>
-      <c r="T97" s="1" t="inlineStr"/>
-      <c r="U97" s="1" t="inlineStr"/>
-      <c r="V97" s="1" t="inlineStr"/>
-      <c r="W97" s="1" t="inlineStr"/>
-      <c r="X97" s="1" t="inlineStr"/>
-      <c r="Y97" s="1" t="inlineStr"/>
-    </row>
-    <row r="98">
-      <c r="A98" s="1" t="inlineStr"/>
-      <c r="B98" s="1" t="inlineStr"/>
-      <c r="C98" s="1" t="inlineStr"/>
-      <c r="D98" s="1" t="inlineStr"/>
-      <c r="E98" s="1" t="inlineStr"/>
-      <c r="F98" s="1" t="inlineStr"/>
-      <c r="G98" s="1" t="inlineStr"/>
-      <c r="H98" s="1" t="inlineStr"/>
-      <c r="I98" s="1" t="inlineStr"/>
-      <c r="J98" s="1" t="inlineStr"/>
-      <c r="K98" s="1" t="inlineStr">
-        <is>
-          <t>L1827: stray/suspicious non-ASCII glyph(s): U+20AC EURO SIGN, U+FFFD REPLACEMENT CHARACTER :: When you tell a horse to "get upâ€� look</t>
-        </is>
-      </c>
-      <c r="L98" s="1" t="inlineStr"/>
-      <c r="M98" s="1" t="inlineStr"/>
-      <c r="N98" s="1" t="inlineStr"/>
-      <c r="O98" s="1" t="inlineStr"/>
-      <c r="P98" s="1" t="inlineStr"/>
-      <c r="Q98" s="1" t="inlineStr"/>
-      <c r="R98" s="1" t="inlineStr"/>
-      <c r="S98" s="1" t="inlineStr"/>
-      <c r="T98" s="1" t="inlineStr"/>
-      <c r="U98" s="1" t="inlineStr"/>
-      <c r="V98" s="1" t="inlineStr"/>
-      <c r="W98" s="1" t="inlineStr"/>
-      <c r="X98" s="1" t="inlineStr"/>
-      <c r="Y98" s="1" t="inlineStr"/>
-    </row>
-    <row r="99">
-      <c r="A99" s="1" t="inlineStr"/>
-      <c r="B99" s="1" t="inlineStr"/>
-      <c r="C99" s="1" t="inlineStr"/>
-      <c r="D99" s="1" t="inlineStr"/>
-      <c r="E99" s="1" t="inlineStr"/>
-      <c r="F99" s="1" t="inlineStr"/>
-      <c r="G99" s="1" t="inlineStr"/>
-      <c r="H99" s="1" t="inlineStr"/>
-      <c r="I99" s="1" t="inlineStr"/>
-      <c r="J99" s="1" t="inlineStr"/>
-      <c r="K99" s="1" t="inlineStr">
-        <is>
-          <t>L1851: stray/suspicious non-ASCII glyph(s): U+00A8 DIAERESIS :: is supposed to deliver " such small dÃ¨er" an</t>
-        </is>
-      </c>
-      <c r="L99" s="1" t="inlineStr"/>
-      <c r="M99" s="1" t="inlineStr"/>
-      <c r="N99" s="1" t="inlineStr"/>
-      <c r="O99" s="1" t="inlineStr"/>
-      <c r="P99" s="1" t="inlineStr"/>
-      <c r="Q99" s="1" t="inlineStr"/>
-      <c r="R99" s="1" t="inlineStr"/>
-      <c r="S99" s="1" t="inlineStr"/>
-      <c r="T99" s="1" t="inlineStr"/>
-      <c r="U99" s="1" t="inlineStr"/>
-      <c r="V99" s="1" t="inlineStr"/>
-      <c r="W99" s="1" t="inlineStr"/>
-      <c r="X99" s="1" t="inlineStr"/>
-      <c r="Y99" s="1" t="inlineStr"/>
-    </row>
-    <row r="100">
-      <c r="A100" s="1" t="inlineStr"/>
-      <c r="B100" s="1" t="inlineStr"/>
-      <c r="C100" s="1" t="inlineStr"/>
-      <c r="D100" s="1" t="inlineStr"/>
-      <c r="E100" s="1" t="inlineStr"/>
-      <c r="F100" s="1" t="inlineStr"/>
-      <c r="G100" s="1" t="inlineStr"/>
-      <c r="H100" s="1" t="inlineStr"/>
-      <c r="I100" s="1" t="inlineStr"/>
-      <c r="J100" s="1" t="inlineStr"/>
-      <c r="K100" s="1" t="inlineStr">
-        <is>
-          <t>L1864: stray/suspicious non-ASCII glyph(s): U+20AC EURO SIGN :: A TRUANT PROTEGE.â€”The London Daily</t>
-        </is>
-      </c>
-      <c r="L100" s="1" t="inlineStr"/>
-      <c r="M100" s="1" t="inlineStr"/>
-      <c r="N100" s="1" t="inlineStr"/>
-      <c r="O100" s="1" t="inlineStr"/>
-      <c r="P100" s="1" t="inlineStr"/>
-      <c r="Q100" s="1" t="inlineStr"/>
-      <c r="R100" s="1" t="inlineStr"/>
-      <c r="S100" s="1" t="inlineStr"/>
-      <c r="T100" s="1" t="inlineStr"/>
-      <c r="U100" s="1" t="inlineStr"/>
-      <c r="V100" s="1" t="inlineStr"/>
-      <c r="W100" s="1" t="inlineStr"/>
-      <c r="X100" s="1" t="inlineStr"/>
-      <c r="Y100" s="1" t="inlineStr"/>
-    </row>
-    <row r="101">
-      <c r="A101" s="1" t="inlineStr"/>
-      <c r="B101" s="1" t="inlineStr"/>
-      <c r="C101" s="1" t="inlineStr"/>
-      <c r="D101" s="1" t="inlineStr"/>
-      <c r="E101" s="1" t="inlineStr"/>
-      <c r="F101" s="1" t="inlineStr"/>
-      <c r="G101" s="1" t="inlineStr"/>
-      <c r="H101" s="1" t="inlineStr"/>
-      <c r="I101" s="1" t="inlineStr"/>
-      <c r="J101" s="1" t="inlineStr"/>
-      <c r="K101" s="1" t="inlineStr">
-        <is>
-          <t>L1937: stray/suspicious non-ASCII glyph(s): U+20AC EURO SIGN :: THE SEASON AT NIAGARA FALLS.â€”We learn</t>
-        </is>
-      </c>
-      <c r="L101" s="1" t="inlineStr"/>
-      <c r="M101" s="1" t="inlineStr"/>
-      <c r="N101" s="1" t="inlineStr"/>
-      <c r="O101" s="1" t="inlineStr"/>
-      <c r="P101" s="1" t="inlineStr"/>
-      <c r="Q101" s="1" t="inlineStr"/>
-      <c r="R101" s="1" t="inlineStr"/>
-      <c r="S101" s="1" t="inlineStr"/>
-      <c r="T101" s="1" t="inlineStr"/>
-      <c r="U101" s="1" t="inlineStr"/>
-      <c r="V101" s="1" t="inlineStr"/>
-      <c r="W101" s="1" t="inlineStr"/>
-      <c r="X101" s="1" t="inlineStr"/>
-      <c r="Y101" s="1" t="inlineStr"/>
-    </row>
-    <row r="102">
-      <c r="A102" s="1" t="inlineStr"/>
-      <c r="B102" s="1" t="inlineStr"/>
-      <c r="C102" s="1" t="inlineStr"/>
-      <c r="D102" s="1" t="inlineStr"/>
-      <c r="E102" s="1" t="inlineStr"/>
-      <c r="F102" s="1" t="inlineStr"/>
-      <c r="G102" s="1" t="inlineStr"/>
-      <c r="H102" s="1" t="inlineStr"/>
-      <c r="I102" s="1" t="inlineStr"/>
-      <c r="J102" s="1" t="inlineStr"/>
-      <c r="K102" s="1" t="inlineStr">
-        <is>
-          <t>L1938: stray/suspicious non-ASCII glyph(s): U+20AC EURO SIGN :: from the new paperâ€”the Registerâ€”that the</t>
-        </is>
-      </c>
-      <c r="L102" s="1" t="inlineStr"/>
-      <c r="M102" s="1" t="inlineStr"/>
-      <c r="N102" s="1" t="inlineStr"/>
-      <c r="O102" s="1" t="inlineStr"/>
-      <c r="P102" s="1" t="inlineStr"/>
-      <c r="Q102" s="1" t="inlineStr"/>
-      <c r="R102" s="1" t="inlineStr"/>
-      <c r="S102" s="1" t="inlineStr"/>
-      <c r="T102" s="1" t="inlineStr"/>
-      <c r="U102" s="1" t="inlineStr"/>
-      <c r="V102" s="1" t="inlineStr"/>
-      <c r="W102" s="1" t="inlineStr"/>
-      <c r="X102" s="1" t="inlineStr"/>
-      <c r="Y102" s="1" t="inlineStr"/>
-    </row>
-    <row r="103">
-      <c r="A103" s="1" t="inlineStr"/>
-      <c r="B103" s="1" t="inlineStr"/>
-      <c r="C103" s="1" t="inlineStr"/>
-      <c r="D103" s="1" t="inlineStr"/>
-      <c r="E103" s="1" t="inlineStr"/>
-      <c r="F103" s="1" t="inlineStr"/>
-      <c r="G103" s="1" t="inlineStr"/>
-      <c r="H103" s="1" t="inlineStr"/>
-      <c r="I103" s="1" t="inlineStr"/>
-      <c r="J103" s="1" t="inlineStr"/>
-      <c r="K103" s="1" t="inlineStr">
-        <is>
-          <t>L1966: stray/suspicious non-ASCII glyph(s): U+20AC EURO SIGN, U+2122 TRADE MARK SIGN :: friends, adjourned to Capt. Williamâ€™s Hotel,</t>
-        </is>
-      </c>
-      <c r="L103" s="1" t="inlineStr"/>
-      <c r="M103" s="1" t="inlineStr"/>
-      <c r="N103" s="1" t="inlineStr"/>
-      <c r="O103" s="1" t="inlineStr"/>
-      <c r="P103" s="1" t="inlineStr"/>
-      <c r="Q103" s="1" t="inlineStr"/>
-      <c r="R103" s="1" t="inlineStr"/>
-      <c r="S103" s="1" t="inlineStr"/>
-      <c r="T103" s="1" t="inlineStr"/>
-      <c r="U103" s="1" t="inlineStr"/>
-      <c r="V103" s="1" t="inlineStr"/>
-      <c r="W103" s="1" t="inlineStr"/>
-      <c r="X103" s="1" t="inlineStr"/>
-      <c r="Y103" s="1" t="inlineStr"/>
-    </row>
-    <row r="104">
-      <c r="A104" s="1" t="inlineStr"/>
-      <c r="B104" s="1" t="inlineStr"/>
-      <c r="C104" s="1" t="inlineStr"/>
-      <c r="D104" s="1" t="inlineStr"/>
-      <c r="E104" s="1" t="inlineStr"/>
-      <c r="F104" s="1" t="inlineStr"/>
-      <c r="G104" s="1" t="inlineStr"/>
-      <c r="H104" s="1" t="inlineStr"/>
-      <c r="I104" s="1" t="inlineStr"/>
-      <c r="J104" s="1" t="inlineStr"/>
-      <c r="K104" s="1" t="inlineStr">
-        <is>
-          <t>L1971: stray/suspicious non-ASCII glyph(s): U+20AC EURO SIGN :: Van Wagoner, Chambers, Jardine, andâ€”</t>
-        </is>
-      </c>
-      <c r="L104" s="1" t="inlineStr"/>
-      <c r="M104" s="1" t="inlineStr"/>
-      <c r="N104" s="1" t="inlineStr"/>
-      <c r="O104" s="1" t="inlineStr"/>
-      <c r="P104" s="1" t="inlineStr"/>
-      <c r="Q104" s="1" t="inlineStr"/>
-      <c r="R104" s="1" t="inlineStr"/>
-      <c r="S104" s="1" t="inlineStr"/>
-      <c r="T104" s="1" t="inlineStr"/>
-      <c r="U104" s="1" t="inlineStr"/>
-      <c r="V104" s="1" t="inlineStr"/>
-      <c r="W104" s="1" t="inlineStr"/>
-      <c r="X104" s="1" t="inlineStr"/>
-      <c r="Y104" s="1" t="inlineStr"/>
-    </row>
-    <row r="105">
-      <c r="A105" s="1" t="inlineStr"/>
-      <c r="B105" s="1" t="inlineStr"/>
-      <c r="C105" s="1" t="inlineStr"/>
-      <c r="D105" s="1" t="inlineStr"/>
-      <c r="E105" s="1" t="inlineStr"/>
-      <c r="F105" s="1" t="inlineStr"/>
-      <c r="G105" s="1" t="inlineStr"/>
-      <c r="H105" s="1" t="inlineStr"/>
-      <c r="I105" s="1" t="inlineStr"/>
-      <c r="J105" s="1" t="inlineStr"/>
-      <c r="K105" s="1" t="inlineStr">
-        <is>
-          <t>L1973: stray/suspicious non-ASCII glyph(s): U+20AC EURO SIGN, U+2122 TRADE MARK SIGN :: participated in the eveningâ€™s enjoyment, for</t>
-        </is>
-      </c>
-      <c r="L105" s="1" t="inlineStr"/>
-      <c r="M105" s="1" t="inlineStr"/>
-      <c r="N105" s="1" t="inlineStr"/>
-      <c r="O105" s="1" t="inlineStr"/>
-      <c r="P105" s="1" t="inlineStr"/>
-      <c r="Q105" s="1" t="inlineStr"/>
-      <c r="R105" s="1" t="inlineStr"/>
-      <c r="S105" s="1" t="inlineStr"/>
-      <c r="T105" s="1" t="inlineStr"/>
-      <c r="U105" s="1" t="inlineStr"/>
-      <c r="V105" s="1" t="inlineStr"/>
-      <c r="W105" s="1" t="inlineStr"/>
-      <c r="X105" s="1" t="inlineStr"/>
-      <c r="Y105" s="1" t="inlineStr"/>
-    </row>
-    <row r="106">
-      <c r="A106" s="1" t="inlineStr"/>
-      <c r="B106" s="1" t="inlineStr"/>
-      <c r="C106" s="1" t="inlineStr"/>
-      <c r="D106" s="1" t="inlineStr"/>
-      <c r="E106" s="1" t="inlineStr"/>
-      <c r="F106" s="1" t="inlineStr"/>
-      <c r="G106" s="1" t="inlineStr"/>
-      <c r="H106" s="1" t="inlineStr"/>
-      <c r="I106" s="1" t="inlineStr"/>
-      <c r="J106" s="1" t="inlineStr"/>
-      <c r="K106" s="1" t="inlineStr">
-        <is>
-          <t>L2036: stray/suspicious non-ASCII glyph(s): U+20AC EURO SIGN :: THE RECOVERY OF SUNKEN TREASURE.â€”The</t>
-        </is>
-      </c>
-      <c r="L106" s="1" t="inlineStr"/>
-      <c r="M106" s="1" t="inlineStr"/>
-      <c r="N106" s="1" t="inlineStr"/>
-      <c r="O106" s="1" t="inlineStr"/>
-      <c r="P106" s="1" t="inlineStr"/>
-      <c r="Q106" s="1" t="inlineStr"/>
-      <c r="R106" s="1" t="inlineStr"/>
-      <c r="S106" s="1" t="inlineStr"/>
-      <c r="T106" s="1" t="inlineStr"/>
-      <c r="U106" s="1" t="inlineStr"/>
-      <c r="V106" s="1" t="inlineStr"/>
-      <c r="W106" s="1" t="inlineStr"/>
-      <c r="X106" s="1" t="inlineStr"/>
-      <c r="Y106" s="1" t="inlineStr"/>
-    </row>
-    <row r="107">
-      <c r="A107" s="1" t="inlineStr"/>
-      <c r="B107" s="1" t="inlineStr"/>
-      <c r="C107" s="1" t="inlineStr"/>
-      <c r="D107" s="1" t="inlineStr"/>
-      <c r="E107" s="1" t="inlineStr"/>
-      <c r="F107" s="1" t="inlineStr"/>
-      <c r="G107" s="1" t="inlineStr"/>
-      <c r="H107" s="1" t="inlineStr"/>
-      <c r="I107" s="1" t="inlineStr"/>
-      <c r="J107" s="1" t="inlineStr"/>
-      <c r="K107" s="1" t="inlineStr">
-        <is>
-          <t>L2068: stray/suspicious non-ASCII glyph(s): U+20AC EURO SIGN, U+2122 TRADE MARK SIGN :: Britainâ€™, Guatemala, Hawaii, Hayti, Hon-</t>
-        </is>
-      </c>
-      <c r="L107" s="1" t="inlineStr"/>
-      <c r="M107" s="1" t="inlineStr"/>
-      <c r="N107" s="1" t="inlineStr"/>
-      <c r="O107" s="1" t="inlineStr"/>
-      <c r="P107" s="1" t="inlineStr"/>
-      <c r="Q107" s="1" t="inlineStr"/>
-      <c r="R107" s="1" t="inlineStr"/>
-      <c r="S107" s="1" t="inlineStr"/>
-      <c r="T107" s="1" t="inlineStr"/>
-      <c r="U107" s="1" t="inlineStr"/>
-      <c r="V107" s="1" t="inlineStr"/>
-      <c r="W107" s="1" t="inlineStr"/>
-      <c r="X107" s="1" t="inlineStr"/>
-      <c r="Y107" s="1" t="inlineStr"/>
-    </row>
-    <row r="108">
-      <c r="A108" s="1" t="inlineStr"/>
-      <c r="B108" s="1" t="inlineStr"/>
-      <c r="C108" s="1" t="inlineStr"/>
-      <c r="D108" s="1" t="inlineStr"/>
-      <c r="E108" s="1" t="inlineStr"/>
-      <c r="F108" s="1" t="inlineStr"/>
-      <c r="G108" s="1" t="inlineStr"/>
-      <c r="H108" s="1" t="inlineStr"/>
-      <c r="I108" s="1" t="inlineStr"/>
-      <c r="J108" s="1" t="inlineStr"/>
-      <c r="K108" s="1" t="inlineStr">
-        <is>
-          <t>L2077: stray/suspicious non-ASCII glyph(s): U+20AC EURO SIGN | suspicious token(s): JanVIS (odd internal casing) :: FIRE AT JanVIS.â€”Yesterday afternoon be-</t>
-        </is>
-      </c>
-      <c r="L108" s="1" t="inlineStr"/>
-      <c r="M108" s="1" t="inlineStr"/>
-      <c r="N108" s="1" t="inlineStr"/>
-      <c r="O108" s="1" t="inlineStr"/>
-      <c r="P108" s="1" t="inlineStr"/>
-      <c r="Q108" s="1" t="inlineStr"/>
-      <c r="R108" s="1" t="inlineStr"/>
-      <c r="S108" s="1" t="inlineStr"/>
-      <c r="T108" s="1" t="inlineStr"/>
-      <c r="U108" s="1" t="inlineStr"/>
-      <c r="V108" s="1" t="inlineStr"/>
-      <c r="W108" s="1" t="inlineStr"/>
-      <c r="X108" s="1" t="inlineStr"/>
-      <c r="Y108" s="1" t="inlineStr"/>
-    </row>
-    <row r="109">
-      <c r="A109" s="1" t="inlineStr"/>
-      <c r="B109" s="1" t="inlineStr"/>
-      <c r="C109" s="1" t="inlineStr"/>
-      <c r="D109" s="1" t="inlineStr"/>
-      <c r="E109" s="1" t="inlineStr"/>
-      <c r="F109" s="1" t="inlineStr"/>
-      <c r="G109" s="1" t="inlineStr"/>
-      <c r="H109" s="1" t="inlineStr"/>
-      <c r="I109" s="1" t="inlineStr"/>
-      <c r="J109" s="1" t="inlineStr"/>
-      <c r="K109" s="1" t="inlineStr">
-        <is>
-          <t>L2098: stray/suspicious non-ASCII glyph(s): U+20AC EURO SIGN :: JUNE.â€”Ovid, in his Fasti, makes Juno</t>
-        </is>
-      </c>
-      <c r="L109" s="1" t="inlineStr"/>
-      <c r="M109" s="1" t="inlineStr"/>
-      <c r="N109" s="1" t="inlineStr"/>
-      <c r="O109" s="1" t="inlineStr"/>
-      <c r="P109" s="1" t="inlineStr"/>
-      <c r="Q109" s="1" t="inlineStr"/>
-      <c r="R109" s="1" t="inlineStr"/>
-      <c r="S109" s="1" t="inlineStr"/>
-      <c r="T109" s="1" t="inlineStr"/>
-      <c r="U109" s="1" t="inlineStr"/>
-      <c r="V109" s="1" t="inlineStr"/>
-      <c r="W109" s="1" t="inlineStr"/>
-      <c r="X109" s="1" t="inlineStr"/>
-      <c r="Y109" s="1" t="inlineStr"/>
-    </row>
-    <row r="110">
-      <c r="A110" s="1" t="inlineStr"/>
-      <c r="B110" s="1" t="inlineStr"/>
-      <c r="C110" s="1" t="inlineStr"/>
-      <c r="D110" s="1" t="inlineStr"/>
-      <c r="E110" s="1" t="inlineStr"/>
-      <c r="F110" s="1" t="inlineStr"/>
-      <c r="G110" s="1" t="inlineStr"/>
-      <c r="H110" s="1" t="inlineStr"/>
-      <c r="I110" s="1" t="inlineStr"/>
-      <c r="J110" s="1" t="inlineStr"/>
-      <c r="K110" s="1" t="inlineStr">
-        <is>
-          <t>L2106: stray/suspicious non-ASCII glyph(s): U+20AC EURO SIGN :: a Jumoribusâ€”that is, to the junior or infe-</t>
-        </is>
-      </c>
-      <c r="L110" s="1" t="inlineStr"/>
-      <c r="M110" s="1" t="inlineStr"/>
-      <c r="N110" s="1" t="inlineStr"/>
-      <c r="O110" s="1" t="inlineStr"/>
-      <c r="P110" s="1" t="inlineStr"/>
-      <c r="Q110" s="1" t="inlineStr"/>
-      <c r="R110" s="1" t="inlineStr"/>
-      <c r="S110" s="1" t="inlineStr"/>
-      <c r="T110" s="1" t="inlineStr"/>
-      <c r="U110" s="1" t="inlineStr"/>
-      <c r="V110" s="1" t="inlineStr"/>
-      <c r="W110" s="1" t="inlineStr"/>
-      <c r="X110" s="1" t="inlineStr"/>
-      <c r="Y110" s="1" t="inlineStr"/>
-    </row>
-    <row r="111">
-      <c r="A111" s="1" t="inlineStr"/>
-      <c r="B111" s="1" t="inlineStr"/>
-      <c r="C111" s="1" t="inlineStr"/>
-      <c r="D111" s="1" t="inlineStr"/>
-      <c r="E111" s="1" t="inlineStr"/>
-      <c r="F111" s="1" t="inlineStr"/>
-      <c r="G111" s="1" t="inlineStr"/>
-      <c r="H111" s="1" t="inlineStr"/>
-      <c r="I111" s="1" t="inlineStr"/>
-      <c r="J111" s="1" t="inlineStr"/>
-      <c r="K111" s="1" t="inlineStr">
-        <is>
-          <t>L2114: stray/suspicious non-ASCII glyph(s): U+00A6 BROKEN BAR :: CÃ¦sar ; since which time it has remained un-</t>
-        </is>
-      </c>
-      <c r="L111" s="1" t="inlineStr"/>
-      <c r="M111" s="1" t="inlineStr"/>
-      <c r="N111" s="1" t="inlineStr"/>
-      <c r="O111" s="1" t="inlineStr"/>
-      <c r="P111" s="1" t="inlineStr"/>
-      <c r="Q111" s="1" t="inlineStr"/>
-      <c r="R111" s="1" t="inlineStr"/>
-      <c r="S111" s="1" t="inlineStr"/>
-      <c r="T111" s="1" t="inlineStr"/>
-      <c r="U111" s="1" t="inlineStr"/>
-      <c r="V111" s="1" t="inlineStr"/>
-      <c r="W111" s="1" t="inlineStr"/>
-      <c r="X111" s="1" t="inlineStr"/>
-      <c r="Y111" s="1" t="inlineStr"/>
-    </row>
-    <row r="112">
-      <c r="A112" s="1" t="inlineStr"/>
-      <c r="B112" s="1" t="inlineStr"/>
-      <c r="C112" s="1" t="inlineStr"/>
-      <c r="D112" s="1" t="inlineStr"/>
-      <c r="E112" s="1" t="inlineStr"/>
-      <c r="F112" s="1" t="inlineStr"/>
-      <c r="G112" s="1" t="inlineStr"/>
-      <c r="H112" s="1" t="inlineStr"/>
-      <c r="I112" s="1" t="inlineStr"/>
-      <c r="J112" s="1" t="inlineStr"/>
-      <c r="K112" s="1" t="inlineStr">
-        <is>
-          <t>L2136: stray/suspicious non-ASCII glyph(s): U+20AC EURO SIGN, U+2122 TRADE MARK SIGN :: workshop, office desk or merchantsâ€™ coun-</t>
-        </is>
-      </c>
-      <c r="L112" s="1" t="inlineStr"/>
-      <c r="M112" s="1" t="inlineStr"/>
-      <c r="N112" s="1" t="inlineStr"/>
-      <c r="O112" s="1" t="inlineStr"/>
-      <c r="P112" s="1" t="inlineStr"/>
-      <c r="Q112" s="1" t="inlineStr"/>
-      <c r="R112" s="1" t="inlineStr"/>
-      <c r="S112" s="1" t="inlineStr"/>
-      <c r="T112" s="1" t="inlineStr"/>
-      <c r="U112" s="1" t="inlineStr"/>
-      <c r="V112" s="1" t="inlineStr"/>
-      <c r="W112" s="1" t="inlineStr"/>
-      <c r="X112" s="1" t="inlineStr"/>
-      <c r="Y112" s="1" t="inlineStr"/>
-    </row>
-    <row r="113">
-      <c r="A113" s="1" t="inlineStr"/>
-      <c r="B113" s="1" t="inlineStr"/>
-      <c r="C113" s="1" t="inlineStr"/>
-      <c r="D113" s="1" t="inlineStr"/>
-      <c r="E113" s="1" t="inlineStr"/>
-      <c r="F113" s="1" t="inlineStr"/>
-      <c r="G113" s="1" t="inlineStr"/>
-      <c r="H113" s="1" t="inlineStr"/>
-      <c r="I113" s="1" t="inlineStr"/>
-      <c r="J113" s="1" t="inlineStr"/>
-      <c r="K113" s="1" t="inlineStr">
-        <is>
-          <t>L2152: stray/suspicious non-ASCII glyph(s): U+20AC EURO SIGN, U+2122 TRADE MARK SIGN :: PAUL BOYTONâ€™S FEAT.</t>
-        </is>
-      </c>
-      <c r="L113" s="1" t="inlineStr"/>
-      <c r="M113" s="1" t="inlineStr"/>
-      <c r="N113" s="1" t="inlineStr"/>
-      <c r="O113" s="1" t="inlineStr"/>
-      <c r="P113" s="1" t="inlineStr"/>
-      <c r="Q113" s="1" t="inlineStr"/>
-      <c r="R113" s="1" t="inlineStr"/>
-      <c r="S113" s="1" t="inlineStr"/>
-      <c r="T113" s="1" t="inlineStr"/>
-      <c r="U113" s="1" t="inlineStr"/>
-      <c r="V113" s="1" t="inlineStr"/>
-      <c r="W113" s="1" t="inlineStr"/>
-      <c r="X113" s="1" t="inlineStr"/>
-      <c r="Y113" s="1" t="inlineStr"/>
-    </row>
-    <row r="114">
-      <c r="A114" s="1" t="inlineStr"/>
-      <c r="B114" s="1" t="inlineStr"/>
-      <c r="C114" s="1" t="inlineStr"/>
-      <c r="D114" s="1" t="inlineStr"/>
-      <c r="E114" s="1" t="inlineStr"/>
-      <c r="F114" s="1" t="inlineStr"/>
-      <c r="G114" s="1" t="inlineStr"/>
-      <c r="H114" s="1" t="inlineStr"/>
-      <c r="I114" s="1" t="inlineStr"/>
-      <c r="J114" s="1" t="inlineStr"/>
-      <c r="K114" s="1" t="inlineStr">
-        <is>
-          <t>L2190: stray/suspicious non-ASCII glyph(s): U+20AC EURO SIGN, U+2122 TRADE MARK SIGN | suspicious token(s): 1cellency (letter/digit mix) :: hands of a Government the power of nomi-1cellencyâ€™s advisers responsible for whatever</t>
-        </is>
-      </c>
-      <c r="L114" s="1" t="inlineStr"/>
-      <c r="M114" s="1" t="inlineStr"/>
-      <c r="N114" s="1" t="inlineStr"/>
-      <c r="O114" s="1" t="inlineStr"/>
-      <c r="P114" s="1" t="inlineStr"/>
-      <c r="Q114" s="1" t="inlineStr"/>
-      <c r="R114" s="1" t="inlineStr"/>
-      <c r="S114" s="1" t="inlineStr"/>
-      <c r="T114" s="1" t="inlineStr"/>
-      <c r="U114" s="1" t="inlineStr"/>
-      <c r="V114" s="1" t="inlineStr"/>
-      <c r="W114" s="1" t="inlineStr"/>
-      <c r="X114" s="1" t="inlineStr"/>
-      <c r="Y114" s="1" t="inlineStr"/>
-    </row>
-    <row r="115">
-      <c r="A115" s="1" t="inlineStr"/>
-      <c r="B115" s="1" t="inlineStr"/>
-      <c r="C115" s="1" t="inlineStr"/>
-      <c r="D115" s="1" t="inlineStr"/>
-      <c r="E115" s="1" t="inlineStr"/>
-      <c r="F115" s="1" t="inlineStr"/>
-      <c r="G115" s="1" t="inlineStr"/>
-      <c r="H115" s="1" t="inlineStr"/>
-      <c r="I115" s="1" t="inlineStr"/>
-      <c r="J115" s="1" t="inlineStr"/>
-      <c r="K115" s="1" t="inlineStr">
-        <is>
-          <t>L2194: stray/suspicious non-ASCII glyph(s): U+20AC EURO SIGN, U+00A2 CENT SIGN | isolated marker/symbol line :: â€¢</t>
-        </is>
-      </c>
-      <c r="L115" s="1" t="inlineStr"/>
-      <c r="M115" s="1" t="inlineStr"/>
-      <c r="N115" s="1" t="inlineStr"/>
-      <c r="O115" s="1" t="inlineStr"/>
-      <c r="P115" s="1" t="inlineStr"/>
-      <c r="Q115" s="1" t="inlineStr"/>
-      <c r="R115" s="1" t="inlineStr"/>
-      <c r="S115" s="1" t="inlineStr"/>
-      <c r="T115" s="1" t="inlineStr"/>
-      <c r="U115" s="1" t="inlineStr"/>
-      <c r="V115" s="1" t="inlineStr"/>
-      <c r="W115" s="1" t="inlineStr"/>
-      <c r="X115" s="1" t="inlineStr"/>
-      <c r="Y115" s="1" t="inlineStr"/>
-    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
